--- a/data_extactor/batch_10_fa/batch_0038_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0038_fa.xlsx
@@ -493,12 +493,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Artists and Related Workers, All Other (هنرمندان و کارکنان مرتبط، سایر)</t>
+          <t>هنرمندان و کارکنان مرتبط، سایر (Artists and Related Workers, All Other)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Artist | Ceramic Artist | Digital Artist | Glass Artist | Illustrator | Mosaic Artist | Muralist | Printmaker | Sculptor | Textile Artist</t>
+          <t>هنرمند | هنرمند سرامیک | هنرمند دیجیتال | هنرمند شیشه | تصویرگر | هنرمند موزائیک‌کاری | دیوارنگار | چاپ‌نگار | مجسمه‌ساز | هنرمند نساجی</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Active Listening | Speaking | Reading Comprehension | Critical Thinking | Monitoring | Writing</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fine Arts | Design | English Language | Communications and Media | Computers and Electronics | Sales and Marketing | History and Archeology | Administration and Management</t>
+          <t>هنرهای زیبا | طراحی | زبان انگلیسی | ارتباطات و رسانه | رایانه و الکترونیک | فروش و بازاریابی | تاریخ و باستان‌شناسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas | Originality | Visualization | Arm-Hand Steadiness | Visual Color Discrimination</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | اصالت | تجسم | ثبات دست و بازو | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Face-to-Face Discussions with Individuals and Within Teams | E-Mail | Telephone Conversations | Indoors, Environmentally Controlled | Contact With Others | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Time Pressure | Level of Competition | Work With or Contribute to a Work Group or Team | Spend Time Sitting | Importance of Being Exact or Accurate | Deal With External Customers or the Public in General | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | سطح رقابت | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Fine Artists, Including Painters, Sculptors, and Illustrators | Craft Artists | Special Effects Artists and Animators | Art Directors | Graphic Designers | Commercial and Industrial Designers | Fashion Designers | Interior Designers | Set and Exhibit Designers | Floral Designers | Merchandise Displayers and Window Trimmers | Designers, All Other | Photographers | Film and Video Editors | Camera Operators, Television, Video, and Film | Art, Drama, and Music Teachers, Postsecondary | Museum Technicians and Conservators | Curators | Self-Enrichment Teachers | Producers and Directors</t>
+          <t>هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | هنرمندان صنایع دستی | هنرمندان جلوه‌های ویژه و انیماتورها | مدیران هنری | طراحان گرافیک | طراحان تجاری و صنعتی | طراحان مد | طراحان داخلی | طراحان صحنه و نمایشگاه | طراحان گل | چیدمان‌کنندگان کالا و تزئین‌کنندگان ویترین | طراحان، سایر | عکاسان | تدوینگران فیلم و ویدئو | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | مدرسان هنر، نمایش و موسیقی، آموزش عالی | تکنسین‌ها و محافظان موزه | موزه‌داران | معلمان خودسازی | تهیه‌کنندگان و کارگردانان</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Create original artworks in media and specialties not classified separately. | Develop concepts, sketches, and prototypes for artistic works. | Select and prepare materials, tools, and techniques appropriate to the medium. | Execute finished works using hand and digital methods. | Confer with clients, galleries, and agents about commissions and requirements. | Estimate materials, time, and costs for commissioned projects. | Photograph and document completed works for portfolios and catalogs. | Market and sell works through exhibitions, galleries, and online channels. | Maintain studio space, equipment, and material inventories. | Frame, mount, package, and ship artworks to clients and venues. | Study art history, trends, and techniques to develop artistic practice. | Prepare proposals and applications for grants, residencies, and public commissions. | Teach workshops and demonstrate techniques to students and the public. | Restore, conserve, or reproduce existing works when commissioned.</t>
+          <t>خلق آثار هنری اصیل در رسانه‌ها و تخصص‌هایی که جداگانه طبقه‌بندی نشده‌اند. | تدوین ایده‌ها، طرح‌های اولیه و نمونه‌های آزمایشی آثار هنری. | انتخاب و آماده‌سازی مواد، ابزارها و فنون متناسب با رسانه هنری. | اجرای آثار نهایی با روش‌های دستی و دیجیتال. | رایزنی با کارفرمایان، نگارخانه‌ها و نمایندگان درباره سفارش‌ها و الزامات آن‌ها. | برآورد مواد، زمان و هزینه پروژه‌های سفارشی. | عکاسی و مستندسازی آثار تکمیل‌شده برای نمونه‌کارها و کاتالوگ‌ها. | بازاریابی و فروش آثار از راه نمایشگاه‌ها، نگارخانه‌ها و بسترهای برخط. | نگهداری فضای کارگاه، تجهیزات و موجودی مواد. | قاب‌بندی، نصب، بسته‌بندی و ارسال آثار هنری به مشتریان و محل‌های نمایش. | مطالعه تاریخ هنر، روندها و فنون برای پرورش شیوه هنری. | تهیه پیشنهادها و درخواست‌ها برای دریافت اعتبار، اقامت هنری و سفارش‌های عمومی. | برگزاری کارگاه آموزشی و نمایش عملی فنون برای هنرجویان و عموم مردم. | مرمت، حفاظت یا بازآفرینی آثار موجود در صورت دریافت سفارش.</t>
         </is>
       </c>
     </row>
@@ -550,42 +550,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Commercial and Industrial Designers (طراحان تجاری و صنعتی)</t>
+          <t>طراحان تجاری و صنعتی (Commercial and Industrial Designers)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Design Engineer | Designer | Industrial Designer | Mechanical Designer | Mold Designer | Product Design Engineer | Product Designer | Product Development Engineer | Sign Designer</t>
+          <t>مهندس طراحی | طراح | طراح صنعتی | طراح مکانیک | طراح قالب | مهندس طراحی محصول | طراح محصول | مهندس توسعه محصول | طراح تابلو</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1CadCam Unigraphics | Adobe Acrobat | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe FreeHand MX | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Apache Maven | Apple iOS | Ashlar-Vellum Cobalt | Autodesk 3ds Max | Autodesk AliasStudio | Autodesk AutoCAD | Autodesk Maya | Autodesk Revit | C | C# | C++ | Cascading style sheets CSS | Chaos Group V-Ray | Corel CorelDraw Graphics Suite | Corel Painter | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Delphi Technology | نرم‌افزار ESRI ArcGIS | Eko | نرم‌افزار ایمیل | Figma | نرم‌افزار تحلیل المان محدود | Geometric CAMWorks | Hypertext markup language HTML | IBM Notes | نرم‌افزار InVision | JavaScript | Kapwing | Maxon Cinema 4D | McNeel Rhinoceros 3D | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft Word | Minitab | National Instruments LabVIEW | PTC Creo Parametric | Python | QuarkXPress | نرم‌افزار SAP | Siemens NX | Siemens UGS NX | نرم‌افزار به عنوان سرویس SaaS | The MathWorks MATLAB | Trimble SketchUp Pro | Verilog | نرم‌افزار مرورگر وب | Xara Designer Pro | jQuery</t>
+          <t>1CadCam Unigraphics | Adobe Acrobat | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe FreeHand MX | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Apache Maven | Apple iOS | Ashlar-Vellum Cobalt | Autodesk 3ds Max | Autodesk AliasStudio | Autodesk AutoCAD | Autodesk Maya | Autodesk Revit | C | C# | C++ | برگه‌های سبک آبشاری CSS | Chaos Group V-Ray | Corel CorelDraw Graphics Suite | Corel Painter | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Delphi Technology | نرم‌افزار ESRI ArcGIS | Eko | نرم‌افزار ایمیل | Figma | نرم‌افزار تحلیل المان محدود | Geometric CAMWorks | زبان نشانه‌گذاری ابرمتن HTML | IBM Notes | نرم‌افزار InVision | JavaScript | Kapwing | Maxon Cinema 4D | McNeel Rhinoceros 3D | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft Word | Minitab | National Instruments LabVIEW | PTC Creo Parametric | Python | QuarkXPress | نرم‌افزار SAP | Siemens NX | Siemens UGS NX | نرم‌افزار به عنوان سرویس SaaS | The MathWorks MATLAB | Trimble SketchUp Pro | Verilog | نرم‌افزار مرورگر وب | Xara Designer Pro | jQuery</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Active Listening | Reading Comprehension | Critical Thinking | Speaking | Writing | Monitoring | Active Learning</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Design | Engineering and Technology | Production and Processing | Mechanical | Computers and Electronics | Mathematics | English Language | Physics | Sales and Marketing | Administrative</t>
+          <t>طراحی | مهندسی و فناوری | تولید و فرآوری | مکانیک | رایانه و الکترونیک | ریاضیات | زبان انگلیسی | فیزیک | فروش و بازاریابی | اداری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fluency of Ideas | Originality | Near Vision | Deductive Reasoning | Visualization | Oral Comprehension | Written Comprehension | Oral Expression | Problem Sensitivity | Information Ordering | Speech Recognition | Speech Clarity | Inductive Reasoning | Visual Color Discrimination | Selective Attention | Flexibility of Closure | Category Flexibility | Written Expression | Far Vision</t>
+          <t>روانی ایده‌ها | اصالت | بینایی نزدیک | استدلال قیاسی | تجسم | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | تشخیص رنگ بصری | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | بیان کتبی | بینایی دور</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>E-Mail | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team | Telephone Conversations | Importance of Being Exact or Accurate | Spend Time Sitting | Contact With Others | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Time Pressure | Deal With External Customers or the Public in General | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Importance of Repeating Same Tasks | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Craft Artists | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronics Drafters | Fabric and Apparel Patternmakers | Fashion Designers | Industrial Engineering Technologists and Technicians | Industrial Engineers | Interior Designers | Layout Workers, Metal and Plastic | Manufacturing Engineers | Materials Engineers | Materials Scientists | Mechanical Drafters | Mechanical Engineering Technologists and Technicians | Mechanical Engineers | Model Makers, Metal and Plastic | Model Makers, Wood | Molders, Shapers, and Casters, Except Metal and Plastic | Patternmakers, Metal and Plastic | Patternmakers, Wood</t>
+          <t>هنرمندان صنایع دستی | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | الگوسازان پارچه و پوشاک | طراحان مد | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | طراحان داخلی | کارگران شابلون‌زنی، فلز و پلاستیک | مهندسان تولید | مهندسان مواد | دانشمندان مواد | نقشه‌کشان مکانیک | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | الگوسازان فلز و پلاستیک | الگوسازان چوب</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Advise corporations on issues involving corporate image projects or problems. | Confer with engineering, marketing, production, or sales departments, or with customers, to establish and evaluate design concepts for manufactured products. | Coordinate the look and function of product lines. | Design graphic material for use as ornamentation, illustration, or advertising on manufactured materials and packaging or containers. | Develop industrial standards and regulatory guidelines. | Develop manufacturing procedures and monitor the manufacture of their designs in a factory to improve operations and product quality. | Direct and coordinate the fabrication of models or samples and the drafting of working drawings and specification sheets from sketches. | Evaluate feasibility of design ideas, based on factors such as appearance, safety, function, serviceability, budget, production costs/methods, and market characteristics. | Fabricate models or samples in paper, wood, glass, fabric, plastic, metal, or other materials, using hand or power tools. | Investigate product characteristics such as the product's safety and handling qualities, its market appeal, how efficiently it can be produced, and ways of distributing, using, and maintaining it. | Modify and refine designs, using working models, to conform with customer specifications, production limitations, or changes in design trends. | Participate in new product planning or market research, including studying the potential need for new products. | Prepare sketches of ideas, detailed drawings, illustrations, artwork, or blueprints, using drafting instruments, paints and brushes, or computer-aided design equipment. | Present designs and reports to customers or design committees for approval and discuss need for modification. | Read publications, attend showings, and study competing products and design styles and motifs to obtain perspective and generate design concepts. | Research production specifications, costs, production materials, and manufacturing methods and provide cost estimates and itemized production requirements. | Supervise assistants' work throughout the design process.</t>
+          <t>ارائه مشاوره به شرکت‌ها در موضوعات مربوط به پروژه‌ها یا مسائل هویت بصری سازمان. | رایزنی با واحدهای مهندسی، بازاریابی، تولید یا فروش، یا با مشتریان، برای تعیین و ارزیابی ایده‌های طراحی محصولات تولیدی. | هماهنگ‌سازی ظاهر و کارکرد خطوط محصول. | طراحی مواد گرافیکی برای استفاده به‌عنوان تزئین، تصویرسازی یا تبلیغات روی کالاهای تولیدی و بسته‌بندی یا ظروف. | تدوین استانداردهای صنعتی و دستورالعمل‌های نظارتی. | تدوین رویه‌های تولید و پایش ساخت طرح‌های خود در کارخانه برای بهبود عملیات و کیفیت محصول. | هدایت و هماهنگی ساخت مدل‌ها یا نمونه‌ها و تهیه نقشه‌های اجرایی و برگه‌های مشخصات از روی طرح‌های اولیه. | ارزیابی امکان‌پذیری ایده‌های طراحی، بر پایه عواملی مانند ظاهر، ایمنی، کارکرد، قابلیت تعمیر، بودجه، هزینه‌ها و روش‌های تولید، و ویژگی‌های بازار. | ساخت مدل یا نمونه از کاغذ، چوب، شیشه، پارچه، پلاستیک، فلز یا سایر مواد، با ابزارهای دستی یا برقی. | بررسی ویژگی‌های محصول مانند ایمنی و کیفیت جابه‌جایی آن، جذابیت بازاری، کارایی تولید، و شیوه‌های توزیع، استفاده و نگهداری آن. | اصلاح و پالایش طرح‌ها با استفاده از مدل‌های اجرایی، برای انطباق با مشخصات مشتری، محدودیت‌های تولید یا تغییر روندهای طراحی. | مشارکت در برنامه‌ریزی محصول جدید یا پژوهش بازار، از جمله بررسی نیاز بالقوه به محصولات جدید. | تهیه طرح‌های اولیه ایده‌ها، نقشه‌های تفصیلی، تصویرسازی، آثار هنری یا نقشه‌های اجرایی، با استفاده از ابزارهای نقشه‌کشی، رنگ و قلم‌مو یا تجهیزات طراحی به کمک رایانه. | ارائه طرح‌ها و گزارش‌ها به مشتریان یا کمیته‌های طراحی برای تأیید و گفت‌وگو درباره لزوم اصلاح. | مطالعه نشریات، حضور در نمایشگاه‌ها و بررسی محصولات رقیب و سبک‌ها و نقش‌مایه‌های طراحی برای کسب دید و پرورش ایده‌های طراحی. | پژوهش درباره مشخصات تولید، هزینه‌ها، مواد اولیه و روش‌های ساخت و ارائه برآورد هزینه و فهرست تفصیلی الزامات تولید. | سرپرستی کار دستیاران در سراسر فرایند طراحی.</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fashion Designers (طراحان مد)</t>
+          <t>طراحان مد (Fashion Designers)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Apparel Designer | Apparel and Accessories Designer | Costume Designer | Designer | Fashion Design Contractor | Fashion Designer | Fashion Graphic Designer | Fashion Stylist | Handbag Designer | Product Developer</t>
+          <t>طراح پوشاک | طراح پوشاک و لوازم جانبی | طراح لباس صحنه | طراح | پیمانکار طراحی مد | طراح مد | طراح گرافیک مد | استایلیست مد | طراح کیف دستی | توسعه‌دهنده محصول</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Active Listening | Speaking | Critical Thinking | Active Learning | Reading Comprehension | Monitoring | Writing | Learning Strategies</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | درک مطلب | نظارت | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Design | Computers and Electronics | Production and Processing | Sales and Marketing | English Language</t>
+          <t>طراحی | رایانه و الکترونیک | تولید و فرآوری | فروش و بازاریابی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Originality | Written Comprehension | Oral Expression | Fluency of Ideas | Visualization | Near Vision | Visual Color Discrimination | Speech Recognition | Oral Comprehension | Category Flexibility | Written Expression | Problem Sensitivity | Deductive Reasoning | Inductive Reasoning | Speech Clarity | Information Ordering | Far Vision | Selective Attention</t>
+          <t>اصالت | درک کتبی | بیان شفاهی | روانی ایده‌ها | تجسم | بینایی نزدیک | تشخیص رنگ بصری | تشخیص گفتار | درک شفاهی | انعطاف‌پذیری دسته‌بندی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی دور | توجه انتخابی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>E-Mail | Time Pressure | Spend Time Sitting | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Work Outcomes and Results of Other Workers | Work With or Contribute to a Work Group or Team</t>
+          <t>ایمیل | فشار زمانی | صرف زمان برای نشستن | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Art Directors | Commercial and Industrial Designers | Costume Attendants | Craft Artists | Fabric and Apparel Patternmakers | Fine Artists, Including Painters, Sculptors, and Illustrators | Floral Designers | Graphic Designers | Interior Designers | Jewelers and Precious Stone and Metal Workers | Makeup Artists, Theatrical and Performance | Merchandise Displayers and Window Trimmers | Painting, Coating, and Decorating Workers | Patternmakers, Metal and Plastic | Retail Salespersons | Set and Exhibit Designers | Sewers, Hand | Sewing Machine Operators | Shoe and Leather Workers and Repairers | Tailors, Dressmakers, and Custom Sewers</t>
+          <t>مدیران هنری | طراحان تجاری و صنعتی | متصدیان لباس | هنرمندان صنایع دستی | الگوسازان پارچه و پوشاک | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گل | طراحان گرافیک | طراحان داخلی | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | میکاپ آرتیست‌های تئاتر و نمایش | چیدمان‌کنندگان کالا و تزئین‌کنندگان ویترین | کارگران نقاشی، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | فروشندگان خرده‌فروشی | طراحان صحنه و نمایشگاه | دوزندگان دستی | اپراتورهای چرخ خیاطی | کارگران و تعمیرکاران کفش و چرم | خیاطان، دوزندگان زنانه و دوزندگان سفارشی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Adapt other designers' ideas for the mass market. | Attend fashion shows and review garment magazines and manuals to gather information about fashion trends and consumer preferences. | Collaborate with other designers to coordinate special products and designs. | Confer with sales and management executives or with clients to discuss design ideas. | Design custom clothing and accessories for individuals, retailers, or theatrical, television, or film productions. | Determine prices for styles. | Develop a group of products or accessories, and market them through venues such as boutiques or mail-order catalogs. | Direct and coordinate workers involved in drawing and cutting patterns and constructing samples or finished garments. | Draw patterns for articles designed, cut patterns, and cut material according to patterns, using measuring instruments and scissors. | Examine sample garments on and off models, modifying designs to achieve desired effects. | Identify target markets for designs, looking at factors such as age, gender, and socioeconomic status. | Provide sample garments to agents and sales representatives, and arrange for showings of sample garments at sales meetings or fashion shows. | Purchase new or used clothing and accessory items as needed to complete designs. | Read scripts and consult directors and other production staff to develop design concepts and plan productions. | Research the styles and periods of clothing needed for film or theatrical productions. | Select materials and production techniques to be used for products. | Sew together sections of material to form mockups or samples of garments or articles, using sewing equipment. | Sketch rough and detailed drawings of apparel or accessories, and write specifications such as color schemes, construction, material types, and accessory requirements. | Test fabrics or oversee testing so that garment care labels can be created. | Visit textile showrooms to keep up-to-date on the latest fabrics.</t>
+          <t>تطبیق ایده‌های سایر طراحان برای بازار انبوه. | حضور در نمایش‌های مد و بررسی مجلات و راهنماهای پوشاک برای گردآوری اطلاعات درباره روندهای مد و ترجیحات مصرف‌کننده. | همکاری با سایر طراحان برای هماهنگی محصولات و طرح‌های ویژه. | رایزنی با مدیران فروش و مدیریت یا با مشتریان برای گفت‌وگو درباره ایده‌های طراحی. | طراحی پوشاک و لوازم جانبی سفارشی برای اشخاص، خرده‌فروشان یا تولیدات تئاتری، تلویزیونی یا سینمایی. | تعیین قیمت برای هر مدل. | تدوین مجموعه‌ای از محصولات یا لوازم جانبی و بازاریابی آن‌ها از راه بسترهایی مانند بوتیک‌ها یا کاتالوگ‌های سفارش پستی. | هدایت و هماهنگی کارکنانی که الگو می‌کشند و برش می‌دهند و نمونه یا پوشاک نهایی را می‌دوزند. | کشیدن الگو برای اقلام طراحی‌شده، برش الگو و برش پارچه مطابق الگو، با استفاده از ابزارهای اندازه‌گیری و قیچی. | بررسی نمونه لباس‌ها روی مدل و بیرون از آن و اصلاح طرح‌ها برای دستیابی به اثر دلخواه. | شناسایی بازارهای هدف طرح‌ها، با در نظر گرفتن عواملی مانند سن، جنسیت و جایگاه اجتماعی‌اقتصادی. | ارائه نمونه لباس به نمایندگان و کارشناسان فروش و ترتیب دادن نمایش نمونه‌ها در جلسات فروش یا نمایش‌های مد. | خرید اقلام پوشاک و لوازم جانبی نو یا دست‌دوم در صورت نیاز برای تکمیل طرح‌ها. | مطالعه فیلم‌نامه و رایزنی با کارگردانان و سایر عوامل تولید برای تدوین ایده‌های طراحی و برنامه‌ریزی تولید. | پژوهش درباره سبک‌ها و دوره‌های تاریخی پوشاک مورد نیاز تولیدات سینمایی یا تئاتری. | انتخاب مواد و فنون تولید مورد استفاده برای محصولات. | دوخت بخش‌های پارچه به یکدیگر برای ساخت ماکت یا نمونه لباس و اقلام، با استفاده از تجهیزات دوخت. | ترسیم طرح‌های اولیه و تفصیلی پوشاک یا لوازم جانبی و نگارش مشخصاتی مانند ترکیب رنگ، شیوه دوخت، نوع پارچه و الزامات لوازم جانبی. | آزمون پارچه‌ها یا نظارت بر آزمون آن‌ها تا برچسب راهنمای نگهداری لباس تهیه شود. | بازدید از نمایشگاه‌های پارچه برای به‌روز ماندن از جدیدترین منسوجات.</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Floral Designers (طراحان گل)</t>
+          <t>طراحان گل (Floral Designers)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Designer | Floral Artist | Floral Clerk | Floral Department Specialist | Floral Designer | Florist | Wedding Decorator</t>
+          <t>طراح | هنرمند گل‌آرایی | متصدی فروش گل | کارشناس بخش گل | طراح گل‌آرایی | گل‌فروش | تزئین‌کننده مراسم ازدواج</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Active Listening | Speaking | Critical Thinking | Active Learning | Monitoring</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Customer and Personal Service | Production and Processing | Sales and Marketing | Design | English Language</t>
+          <t>خدمات مشتری و شخصی | تولید و فرآوری | فروش و بازاریابی | طراحی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Oral Comprehension | Oral Expression | Visualization | Near Vision | Visual Color Discrimination | Originality | Speech Clarity | Category Flexibility | Fluency of Ideas | Information Ordering | Speech Recognition | Far Vision | Trunk Strength | Finger Dexterity | Manual Dexterity | Arm-Hand Steadiness | Deductive Reasoning | Selective Attention | Written Comprehension</t>
+          <t>درک شفاهی | بیان شفاهی | تجسم | بینایی نزدیک | تشخیص رنگ بصری | اصالت | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | ترتیب‌دهی اطلاعات | تشخیص گفتار | بینایی دور | قدرت تنه | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | استدلال قیاسی | توجه انتخابی | درک کتبی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Telephone Conversations | Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Contact With Others | Work With or Contribute to a Work Group or Team | E-Mail | Freedom to Make Decisions | Spend Time Standing | Coordinate or Lead Others in Accomplishing Work Activities | Indoors, Environmentally Controlled | Time Pressure | Work Outcomes and Results of Other Workers | Physical Proximity | Health and Safety of Other Workers | Written Letters and Memos</t>
+          <t>مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | آزادی در تصمیم‌گیری | صرف زمان برای ایستادن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | سلامت و ایمنی سایر کارکنان | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Commercial and Industrial Designers | Craft Artists | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | Fabric and Apparel Patternmakers | Fashion Designers | Fine Artists, Including Painters, Sculptors, and Illustrators | Hairdressers, Hairstylists, and Cosmetologists | Interior Designers | Jewelers and Precious Stone and Metal Workers | Merchandise Displayers and Window Trimmers | Packers and Packagers, Hand | Painting, Coating, and Decorating Workers | Patternmakers, Metal and Plastic | Photographers | Retail Salespersons | Sewers, Hand | Sewing Machine Operators | Shoe and Leather Workers and Repairers | Stockers and Order Fillers | Tailors, Dressmakers, and Custom Sewers</t>
+          <t>طراحان تجاری و صنعتی | هنرمندان صنایع دستی | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | الگوسازان پارچه و پوشاک | طراحان مد | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | آرایشگران زنانه، استایلیست‌های مو و متخصصان زیبایی | طراحان داخلی | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | چیدمان‌کنندگان کالا و تزئین‌کنندگان ویترین | بسته‌بندهای دستی | کارگران نقاشی، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | عکاسان | فروشندگان خرده‌فروشی | دوزندگان دستی | اپراتورهای چرخ خیاطی | کارگران و تعمیرکاران کفش و چرم | قفسه‌چین‌ها و پرکننده‌های سفارش | خیاطان، دوزندگان زنانه و دوزندگان سفارشی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Conduct classes or demonstrations, or train other workers. | Confer with clients regarding price and type of arrangement desired and the date, time, and place of delivery. | Create and change in-store and window displays, designs, and looks to enhance a shop's image. | Decorate, or supervise the decoration of, buildings, halls, churches, or other facilities for parties, weddings and other occasions. | Deliver arrangements to customers, or oversee employees responsible for deliveries. | Inform customers about the care, maintenance, and handling of various flowers and foliage, indoor plants, and other items. | Order and purchase flowers and supplies from wholesalers and growers. | Perform general cleaning duties in the store to ensure the shop is clean and tidy. | Perform office and retail service duties, such as keeping financial records, serving customers, answering telephones, selling giftware items, and receiving payment. | Plan arrangement according to client's requirements, using knowledge of design and properties of materials, or select appropriate standard design pattern. | Select flora and foliage for arrangements, working with numerous combinations to synthesize and develop new creations. | Trim material and arrange bouquets, wreaths, terrariums, and other items, using trimmers, shapers, wire, pins, floral tape, foam, and other materials. | Unpack stock as it comes into the shop. | Water plants, and cut, condition, and clean flowers and foliage for storage. | Wrap and price completed arrangements.</t>
+          <t>برگزاری کلاس یا نمایش عملی، یا آموزش سایر کارکنان. | رایزنی با مشتریان درباره قیمت و نوع آرایش گل مورد نظر و تاریخ، زمان و محل تحویل. | ایجاد و تغییر ویترین و چیدمان داخلی فروشگاه، طرح‌ها و ظاهر آن برای ارتقای تصویر مغازه. | تزئین ساختمان‌ها، سالن‌ها، اماکن مذهبی یا سایر مکان‌ها برای مهمانی، مراسم ازدواج و سایر مناسبت‌ها، یا سرپرستی این تزئینات. | تحویل آرایش‌های گل به مشتریان، یا نظارت بر کارکنان مسئول تحویل. | آگاه‌سازی مشتریان درباره مراقبت، نگهداری و جابه‌جایی گل‌ها و شاخ‌وبرگ‌های گوناگون، گیاهان آپارتمانی و سایر اقلام. | سفارش و خرید گل و ملزومات از عمده‌فروشان و پرورش‌دهندگان. | انجام امور عمومی نظافت فروشگاه برای اطمینان از تمیزی و مرتب بودن مغازه. | انجام وظایف اداری و خدمات خرده‌فروشی، مانند نگهداری سوابق مالی، خدمت به مشتریان، پاسخ‌گویی تلفنی، فروش اقلام هدیه و دریافت وجه. | طراحی آرایش گل مطابق خواسته مشتری، با به‌کارگیری دانش طراحی و ویژگی‌های مواد، یا انتخاب الگوی طراحی استاندارد مناسب. | انتخاب گل و شاخ‌وبرگ برای آرایش‌ها، با کار روی ترکیب‌های متعدد برای ساخت و پرورش خلاقیت‌های تازه. | پیرایش مواد و آماده‌سازی دسته‌گل، تاج گل، تراریوم و سایر اقلام، با استفاده از قیچی، قالب، مفتول، سنجاق، چسب گل، فوم و سایر مواد. | بازکردن بسته‌های کالا هنگام ورود به مغازه. | آبیاری گیاهان و برش، آماده‌سازی و تمیز کردن گل و شاخ‌وبرگ برای نگهداری. | بسته‌بندی و قیمت‌گذاری آرایش‌های آماده‌شده.</t>
         </is>
       </c>
     </row>
@@ -721,42 +721,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Graphic Designers (طراحان گرافیک)</t>
+          <t>طراحان گرافیک (Graphic Designers)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Artist | Brand Designer | Designer | Graphic Artist | Graphic Design Coordinator | Graphic Designer | Online Producer | Production Artist | Publications Designer | Technical Illustrator</t>
+          <t>هنرمند | طراح برند | طراح | هنرمند گرافیک | هماهنگ‌کننده طراحی گرافیک | طراح گرافیک | تهیه‌کننده برخط | هنرمند تولید | طراح نشریات | تصویرگر فنی</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AJAX | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | Adobe ColdFusion | نرم‌افزار Adobe Creative Cloud | Adobe Distiller | Adobe Dreamweaver | Adobe FrameMaker | Adobe FreeHand MX | Adobe Illustrator | Adobe InDesign | Adobe Macromedia HomeSite | Adobe PageMaker | Adobe Photoshop | Adobe Premiere Pro | Apple Final Cut Pro | Apple Keynote | Apple iMovie | Apple iWork Keynote | Apple macOS | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | Avid Pro Tools | Bentley MicroStation | Canva | Cascading style sheets CSS | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Corel CorelDraw Graphics Suite | Corel WordPerfect Office Suite | Dassault Systemes CATIA | Drupal | Dynamic hypertext markup language DHTML | Extensible hypertext markup language XHTML | Extensible markup language XML | Facebook | Figma | FileMaker Pro | Google Ads | Google Chrome | Google Docs | Google Drive | Google Slides | Hypertext markup language HTML | IBM Notes | Intuit QuickBooks | JavaScript | LinkedIn | Maxon Cinema 4D | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft Visio | Microsoft Windows | Microsoft Word | Nuance OmniPage Professional | Oracle Eloqua | Oracle JavaServer Pages JSP | PDF readers | PHP | PTC Creo Parametric | QuarkXPress | SignCAD Systems SignCAD | SmugMug Flickr | Social media sites | Structured query language SQL | Trimble SketchUp Pro | Verilog | WeVideo | نرم‌افزار مرورگر وب | WordPress | YouTube | jQuery</t>
+          <t>AJAX | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | Adobe ColdFusion | نرم‌افزار Adobe Creative Cloud | Adobe Distiller | Adobe Dreamweaver | Adobe FrameMaker | Adobe FreeHand MX | Adobe Illustrator | Adobe InDesign | Adobe Macromedia HomeSite | Adobe PageMaker | Adobe Photoshop | Adobe Premiere Pro | Apple Final Cut Pro | Apple Keynote | Apple iMovie | Apple iWork Keynote | Apple macOS | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | Avid Pro Tools | Bentley MicroStation | Canva | برگه‌های سبک آبشاری CSS | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Corel CorelDraw Graphics Suite | Corel WordPerfect Office Suite | Dassault Systemes CATIA | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | Facebook | Figma | FileMaker Pro | Google Ads | Google Chrome | Google Docs | Google Drive | Google Slides | زبان نشانه‌گذاری ابرمتن HTML | IBM Notes | Intuit QuickBooks | JavaScript | LinkedIn | Maxon Cinema 4D | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft Visio | Microsoft Windows | Microsoft Word | Nuance OmniPage Professional | Oracle Eloqua | Oracle JavaServer Pages JSP | خواننده‌های PDF | PHP | PTC Creo Parametric | QuarkXPress | SignCAD Systems SignCAD | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | زبان پرس‌وجوی ساختاریافته SQL | Trimble SketchUp Pro | Verilog | WeVideo | نرم‌افزار مرورگر وب | WordPress | YouTube | jQuery</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Active Listening | Speaking | Active Learning | Critical Thinking | Writing | Reading Comprehension | Monitoring</t>
+          <t>گوش دادن فعال | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | درک مطلب | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Design | Computers and Electronics | Fine Arts | Communications and Media | English Language | Sales and Marketing | Customer and Personal Service | Production and Processing | Administration and Management</t>
+          <t>طراحی | رایانه و الکترونیک | هنرهای زیبا | ارتباطات و رسانه | زبان انگلیسی | فروش و بازاریابی | خدمات مشتری و شخصی | تولید و فرآوری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Originality | Fluency of Ideas | Near Vision | Written Comprehension | Oral Comprehension | Written Expression | Oral Expression | Visual Color Discrimination | Speech Recognition | Speech Clarity | Deductive Reasoning | Information Ordering | Inductive Reasoning | Problem Sensitivity | Visualization | Selective Attention | Category Flexibility</t>
+          <t>اصالت | روانی ایده‌ها | بینایی نزدیک | درک کتبی | درک شفاهی | بیان کتبی | بیان شفاهی | تشخیص رنگ بصری | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | تجسم | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>E-Mail | Spend Time Sitting | Time Pressure | Telephone Conversations | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Level of Competition | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Spend Time Making Repetitive Motions | Importance of Repeating Same Tasks | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls</t>
+          <t>ایمیل | صرف زمان برای نشستن | فشار زمانی | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | سطح رقابت | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | اهمیت تکرار وظایف یکسان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Art Directors | Commercial and Industrial Designers | Craft Artists | Desktop Publishers | Fabric and Apparel Patternmakers | Fashion Designers | Film and Video Editors | Fine Artists, Including Painters, Sculptors, and Illustrators | Interior Designers | Merchandise Displayers and Window Trimmers | Photographers | Prepress Technicians and Workers | Producers and Directors | Set and Exhibit Designers | Software Developers | Special Effects Artists and Animators | Video Game Designers | Web Developers | Web and Digital Interface Designers | Writers and Authors</t>
+          <t>مدیران هنری | طراحان تجاری و صنعتی | هنرمندان صنایع دستی | ناشران رومیزی | الگوسازان پارچه و پوشاک | طراحان مد | تدوینگران فیلم و ویدئو | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان داخلی | چیدمان‌کنندگان کالا و تزئین‌کنندگان ویترین | عکاسان | تکنسین‌ها و کارگران پیش از چاپ | تهیه‌کنندگان و کارگردانان | طراحان صحنه و نمایشگاه | توسعه‌دهندگان نرم‌افزار | هنرمندان جلوه‌های ویژه و انیماتورها | طراحان بازی‌های ویدئویی | توسعه‌دهندگان وب | طراحان رابط دیجیتال و وب | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Confer with clients to discuss and determine layout design. | Create designs, concepts, and sample layouts, based on knowledge of layout principles and esthetic design concepts. | Determine size and arrangement of illustrative material and copy, and select style and size of type. | Develop graphics and layouts for product illustrations, company logos, and Web sites. | Draw and print charts, graphs, illustrations, and other artwork, using computer. | Key information into computer equipment to create layouts for client or supervisor. | Maintain archive of images, photos, or previous work products. | Mark up, paste, and assemble final layouts to prepare layouts for printer. | Photograph layouts, using camera, to make layout prints for supervisors or clients. | Prepare digital files for printing. | Prepare illustrations or rough sketches of material, discussing them with clients or supervisors and making necessary changes. | Prepare notes and instructions for workers who assemble and prepare final layouts for printing. | Produce still and animated graphics for on-air and taped portions of television news broadcasts, using electronic video equipment. | Research new software or design concepts. | Research the target audience of projects. | Review final layouts and suggest improvements, as needed. | Study illustrations and photographs to plan presentation of materials, products, or services. | Use computer software to generate new images. | Write or edit copy for clients.</t>
+          <t>رایزنی با مشتریان برای گفت‌وگو و تعیین طراحی چیدمان. | خلق طرح‌ها، ایده‌ها و نمونه چیدمان‌ها، بر پایه دانش اصول صفحه‌آرایی و مفاهیم زیبایی‌شناختی طراحی. | تعیین اندازه و آرایش مواد تصویری و متن، و انتخاب سبک و اندازه قلم. | تدوین گرافیک و چیدمان برای تصویرسازی محصول، نشان‌های شرکتی و وب‌سایت‌ها. | ترسیم و چاپ چارت‌ها، نمودارها، تصویرسازی‌ها و سایر آثار گرافیکی، با استفاده از رایانه. | وارد کردن اطلاعات در تجهیزات رایانه‌ای برای ساخت چیدمان برای مشتری یا سرپرست. | نگهداری بایگانی تصاویر، عکس‌ها یا آثار پیشین. | علامت‌گذاری، چسباندن و مونتاژ چیدمان‌های نهایی برای آماده‌سازی جهت چاپ. | عکاسی از چیدمان‌ها با دوربین برای تهیه نسخه چاپی چیدمان جهت ارائه به سرپرستان یا مشتریان. | آماده‌سازی فایل‌های دیجیتال برای چاپ. | تهیه تصویرسازی یا طرح‌های اولیه مواد، گفت‌وگو درباره آن‌ها با مشتریان یا سرپرستان و اعمال تغییرات لازم. | تهیه یادداشت‌ها و دستورالعمل برای کارکنانی که چیدمان‌های نهایی را برای چاپ مونتاژ و آماده می‌کنند. | تولید گرافیک ثابت و متحرک برای بخش‌های زنده و ضبط‌شده اخبار تلویزیونی، با استفاده از تجهیزات ویدئویی الکترونیکی. | پژوهش درباره نرم‌افزارها یا مفاهیم طراحی جدید. | پژوهش درباره مخاطب هدف پروژه‌ها. | بازبینی چیدمان‌های نهایی و ارائه پیشنهاد برای بهبود، در صورت نیاز. | مطالعه تصویرسازی‌ها و عکس‌ها برای برنامه‌ریزی نحوه ارائه مواد، محصولات یا خدمات. | استفاده از نرم‌افزارهای رایانه‌ای برای تولید تصاویر جدید. | نگارش یا ویرایش متن برای مشتریان.</t>
         </is>
       </c>
     </row>
@@ -778,12 +778,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Interior Designers (طراحان داخلی)</t>
+          <t>طراحان داخلی (Interior Designers)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Certified Kitchen Designer | Color and Materials Designer | Commercial Interior Designer | Decorating Consultant | Designer | Interior Decorator | Interior Design Consultant | Interior Design Coordinator | Interior Designer | Registered Interior Designer</t>
+          <t>طراح آشپزخانه دارای گواهی صلاحیت | طراح رنگ و مواد | طراح داخلی فضاهای تجاری | مشاور دکوراسیون | طراح | دکوراتور داخلی | مشاور طراحی داخلی | هماهنگ‌کننده طراحی داخلی | طراح داخلی | طراح داخلی ثبت‌شده</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Speaking | Active Listening | Reading Comprehension | Critical Thinking | Writing | Active Learning | Monitoring | Mathematics</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Design | Customer and Personal Service | Building and Construction | English Language | Sales and Marketing | Administration and Management | Computers and Electronics | Public Safety and Security | Fine Arts | Administrative | Psychology | Personnel and Human Resources</t>
+          <t>طراحی | خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | زبان انگلیسی | فروش و بازاریابی | مدیریت و اداره | رایانه و الکترونیک | ایمنی و امنیت عمومی | هنرهای زیبا | اداری | روان‌شناسی | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fluency of Ideas | Originality | Oral Comprehension | Oral Expression | Visualization | Near Vision | Written Comprehension | Problem Sensitivity | Visual Color Discrimination | Speech Recognition | Speech Clarity | Written Expression | Deductive Reasoning | Category Flexibility | Inductive Reasoning | Information Ordering | Far Vision | Mathematical Reasoning | Selective Attention</t>
+          <t>روانی ایده‌ها | اصالت | درک شفاهی | بیان شفاهی | تجسم | بینایی نزدیک | درک کتبی | حساسیت به مسئله | تشخیص رنگ بصری | تشخیص گفتار | وضوح گفتار | بیان کتبی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی دور | استدلال ریاضی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Time Pressure | Importance of Being Exact or Accurate | Spend Time Sitting | Deal With External Customers or the Public in General | Determine Tasks, Priorities and Goals | Level of Competition | Freedom to Make Decisions | Written Letters and Memos | Coordinate or Lead Others in Accomplishing Work Activities | Frequency of Decision Making</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | سطح رقابت | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Architects, Except Landscape and Naval | Architectural and Civil Drafters | Art Directors | Carpenters | Carpet Installers | Commercial and Industrial Designers | Craft Artists | Fashion Designers | Furniture Finishers | Graphic Designers | Landscape Architects | Layout Workers, Metal and Plastic | Lighting Technicians | Mechanical Drafters | Merchandise Displayers and Window Trimmers | Model Makers, Wood | Painting, Coating, and Decorating Workers | Plasterers and Stucco Masons | Set and Exhibit Designers | Tile and Stone Setters</t>
+          <t>معماران، به‌جز منظر و دریایی | نقشه‌کشان معماری و عمران | مدیران هنری | نجّاران | نصّابان موکت و فرش | طراحان تجاری و صنعتی | هنرمندان صنایع دستی | طراحان مد | پرداخت‌کاران مبلمان | طراحان گرافیک | معماران منظر | کارگران شابلون‌زنی، فلز و پلاستیک | تکنسین‌های نورپردازی | نقشه‌کشان مکانیک | چیدمان‌کنندگان کالا و تزئین‌کنندگان ویترین | مدل‌سازان چوب | کارگران نقاشی، پوشش‌دهی و تزیین | گچ‌کاران و بناهای سیمان‌کاری | طراحان صحنه و نمایشگاه | کاشی‌کاران و سنگ‌کاران</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Advise client on interior design factors, such as space planning, layout and use of furnishings or equipment, and color coordination. | Confer with client to determine factors affecting planning of interior environments, such as budget, architectural preferences, purpose, and function. | Coordinate with other professionals, such as contractors, architects, engineers, and plumbers, to ensure job success. | Design plans to be safe and to be compliant with the American Disabilities Act (ADA). | Design spaces to be environmentally friendly, using sustainable, recycled materials when feasible. | Estimate material requirements and costs, and present design to client for approval. | Formulate environmental plan to be practical, esthetic, and conducive to intended purposes, such as raising productivity or selling merchandise. | Inspect construction work on site to ensure its adherence to the design plans. | Plan and design interior environments for boats, planes, buses, trains, and other enclosed spaces. | Render design ideas in form of paste-ups or drawings. | Research and explore the use of new materials, technologies, and products to incorporate into designs. | Research health and safety code requirements to inform design. | Review and detail shop drawings for construction plans. | Select or design, and purchase furnishings, art work, and accessories. | Subcontract fabrication, installation, and arrangement of carpeting, fixtures, accessories, draperies, paint and wall coverings, art work, furniture, and related items. | Use computer-aided drafting (CAD) and related software to produce construction documents.</t>
+          <t>ارائه مشاوره به کارفرما درباره عوامل طراحی داخلی، مانند برنامه‌ریزی فضا، چیدمان و استفاده از مبلمان یا تجهیزات، و هماهنگی رنگ. | رایزنی با کارفرما برای تعیین عوامل مؤثر بر برنامه‌ریزی فضاهای داخلی، مانند بودجه، ترجیحات معماری، هدف و کارکرد. | هماهنگی با سایر متخصصان، مانند پیمانکاران، معماران، مهندسان و لوله‌کش‌ها، برای تضمین موفقیت کار. | طراحی نقشه‌ها به‌گونه‌ای که ایمن و منطبق بر الزامات دسترس‌پذیری معلولان (ADA) باشد. | طراحی فضاها به‌شکل سازگار با محیط‌زیست، با استفاده از مواد پایدار و بازیافتی در صورت امکان. | برآورد نیازها و هزینه‌های مواد و ارائه طرح به کارفرما برای تأیید. | تدوین طرح فضا به‌گونه‌ای که کاربردی، زیبا و متناسب با اهداف مورد نظر باشد، مانند افزایش بهره‌وری یا فروش کالا. | بازرسی کار ساخت در محل برای اطمینان از رعایت نقشه‌های طراحی. | برنامه‌ریزی و طراحی فضاهای داخلی قایق، هواپیما، اتوبوس، قطار و سایر فضاهای بسته. | ارائه ایده‌های طراحی در قالب کلاژ یا نقشه. | پژوهش و کاوش درباره استفاده از مواد، فناوری‌ها و محصولات جدید برای به‌کارگیری در طرح‌ها. | پژوهش درباره الزامات آیین‌نامه‌های بهداشت و ایمنی برای پشتیبانی از طراحی. | بازبینی و تهیه جزئیات نقشه‌های کارگاهی برای طرح‌های ساخت. | انتخاب یا طراحی و خرید مبلمان، آثار هنری و لوازم جانبی. | واگذاری ساخت، نصب و چیدمان موکت، تجهیزات ثابت، لوازم جانبی، پرده، رنگ و پوشش دیوار، آثار هنری، مبلمان و اقلام مرتبط به پیمانکاران فرعی. | استفاده از نقشه‌کشی به کمک رایانه (CAD) و نرم‌افزارهای مرتبط برای تولید اسناد اجرایی.</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Merchandise Displayers and Window Trimmers (چیدمان‌کنندگان کالا و تزئین‌کنندگان ویترین)</t>
+          <t>چیدمان‌کنندگان کالا و تزئین‌کنندگان ویترین (Merchandise Displayers and Window Trimmers)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Decorator | Display Associate | Display Decorator | Display Specialist | In-Store Marketing Associate | Merchandiser | Visual Merchandiser (VM) | Visual Merchandising Specialist</t>
+          <t>تزیین‌کننده | همکار چیدمان ویترین | تزئین‌کننده ویترین | کارشناس چیدمان ویترین | همکار بازاریابی درون‌فروشگاهی | چیدمان‌کننده کالا | کارشناس چیدمان بصری کالا (VM) | کارشناس چیدمان بصری کالا</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Active Listening | Critical Thinking | Speaking | Reading Comprehension</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Customer and Personal Service | Sales and Marketing | English Language | Administration and Management</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Visualization | Speech Clarity | Oral Comprehension | Oral Expression | Fluency of Ideas | Speech Recognition | Manual Dexterity | Category Flexibility | Finger Dexterity | Trunk Strength | Near Vision | Far Vision | Visual Color Discrimination | Information Ordering | Originality | Deductive Reasoning | Problem Sensitivity | Extent Flexibility | Stamina | Static Strength | Multilimb Coordination | Arm-Hand Steadiness | Gross Body Coordination | Inductive Reasoning | Written Expression | Written Comprehension</t>
+          <t>تجسم | وضوح گفتار | درک شفاهی | بیان شفاهی | روانی ایده‌ها | تشخیص گفتار | مهارت دستی | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | قدرت تنه | بینایی نزدیک | بینایی دور | تشخیص رنگ بصری | ترتیب‌دهی اطلاعات | اصالت | استدلال قیاسی | حساسیت به مسئله | انعطاف‌پذیری دامنه حرکت | استقامت | قدرت ایستا | هماهنگی چند عضو | ثبات دست و بازو | هماهنگی کلی بدن | استدلال استقرایی | بیان کتبی | درک کتبی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Indoors, Environmentally Controlled | Spend Time Standing | Spend Time Walking or Running | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making | Deal With External Customers or the Public in General | Telephone Conversations | Time Pressure | E-Mail | Determine Tasks, Priorities and Goals | Physical Proximity | Coordinate or Lead Others in Accomplishing Work Activities</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | فشار زمانی | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Advertising Sales Agents | Advertising and Promotions Managers | Art Directors | Commercial and Industrial Designers | Counter and Rental Clerks | Craft Artists | Demonstrators and Product Promoters | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | Fashion Designers | First-Line Supervisors of Retail Sales Workers | Floral Designers | Graphic Designers | Interior Designers | Marketing Managers | Retail Salespersons | Sales Managers | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Set and Exhibit Designers | Stockers and Order Fillers | Wholesale and Retail Buyers, Except Farm Products</t>
+          <t>نمایندگان فروش تبلیغات | مدیران تبلیغات و ترویج | مدیران هنری | طراحان تجاری و صنعتی | کارمندان باجه و اجاره | هنرمندان صنایع دستی | نمایش‌دهندگان و تبلیغ‌کنندگان محصول | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | طراحان مد | سرپرستان رده اول کارکنان فروش خرده‌فروشی | طراحان گل | طراحان گرافیک | طراحان داخلی | مدیران بازاریابی | فروشندگان خرده‌فروشی | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | طراحان صحنه و نمایشگاه | قفسه‌چین‌ها و پرکننده‌های سفارش | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Arrange properties, furniture, merchandise, backdrops, or other accessories, as shown in prepared sketches. | Assemble or set up displays, furniture, or products in store space, using colors, lights, pictures, or other accessories to display the product. | Attend training sessions or corporate planning meetings to obtain new ideas for product launches. | Change or rotate window displays, interior display areas, or signage to reflect changes in inventory or promotion. | Collaborate with others to obtain products or other display items. | Construct or assemble displays or display components from fabric, glass, paper, or plastic, using hand tools or woodworking power tools, according to specifications. | Consult with advertising or sales staff to determine type of merchandise to be featured and time and place for each display. | Consult with store managers, buyers, sales associates, housekeeping staff, or engineering staff to determine appropriate placement of displays or products. | Cut out designs on cardboard, hardboard, or plywood, according to motif of event. | Develop ideas or plans for merchandise displays or window decorations. | Dress mannequins for displays. | Install booths, exhibits, displays, carpets, or drapes, as guided by floor plan of building or specifications. | Install decorations, such as flags, banners, festive lights, or bunting on or in building, street, exhibit hall, or booth. | Instruct sales staff in color coordination of clothing racks or counter displays. | Maintain props, products, or mannequins, inspecting them for imperfections, doing touch-ups, cleaning up after customers, or applying preservative coatings as necessary. | Obtain plans from display designers or display managers and discuss their implementation with clients or supervisors. | Place prices or descriptive signs on backdrops, fixtures, merchandise, or floor. | Plan commercial displays to entice and appeal to customers. | Prepare sketches, floor plans, or models of proposed displays. | Select themes, lighting, colors, or props to be used. | Store, pack, and maintain inventory records of props, products, or display items. | Supervise or train staff members on daily tasks, such as visual merchandising. | Take photographs of displays or signage. | Use computers to produce signage.</t>
+          <t>چیدمان لوازم صحنه، مبلمان، کالا، پس‌زمینه یا سایر لوازم جانبی، مطابق طرح‌های اولیه آماده‌شده. | مونتاژ یا برپایی ویترین، مبلمان یا محصولات در فضای فروشگاه، با استفاده از رنگ، نور، تصویر یا سایر لوازم جانبی برای نمایش محصول. | شرکت در دوره‌های آموزشی یا جلسات برنامه‌ریزی شرکت برای دریافت ایده‌های تازه جهت معرفی محصولات. | تغییر یا جابه‌جایی ویترین‌ها، فضاهای نمایش داخلی یا تابلوها متناسب با تغییر موجودی یا برنامه‌های ترویجی. | همکاری با دیگران برای تأمین محصولات یا سایر اقلام نمایشی. | ساخت یا مونتاژ ویترین‌ها یا اجزای آن‌ها از پارچه، شیشه، کاغذ یا پلاستیک، با ابزارهای دستی یا ابزارهای برقی نجاری، مطابق مشخصات. | رایزنی با کارکنان تبلیغات یا فروش برای تعیین نوع کالای برجسته‌شده و زمان و مکان هر ویترین. | رایزنی با مدیران فروشگاه، خریداران، همکاران فروش، کارکنان خدمات یا کارکنان فنی برای تعیین محل مناسب ویترین‌ها یا محصولات. | برش طرح‌ها روی مقوا، تخته فشرده یا تخته‌سه‌لایی، مطابق نقش‌مایه رویداد. | تدوین ایده‌ها یا طرح‌های ویترین کالا یا تزئین ویترین. | پوشاندن لباس بر مانکن‌ها برای ویترین. | نصب غرفه، نمایشگاه، ویترین، موکت یا پرده، مطابق نقشه طبقات ساختمان یا مشخصات. | نصب تزئینات، مانند پرچم، بنر، چراغ‌های تزئینی یا پارچه‌آرایی روی ساختمان، خیابان، سالن نمایشگاه یا غرفه یا در داخل آن‌ها. | آموزش کارکنان فروش در زمینه هماهنگی رنگ رگال‌های پوشاک یا ویترین‌های پیشخوان. | نگهداری لوازم صحنه، محصولات یا مانکن‌ها، بازرسی آن‌ها از نظر عیب، ترمیم جزئی، نظافت پس از مراجعه مشتریان یا اعمال پوشش‌های محافظ در صورت نیاز. | دریافت نقشه‌ها از طراحان یا مدیران ویترین و گفت‌وگو درباره اجرای آن‌ها با مشتریان یا سرپرستان. | قرار دادن برچسب قیمت یا تابلوهای توضیحی روی پس‌زمینه، تجهیزات ثابت، کالا یا کف. | طراحی ویترین‌های تجاری برای جلب و جذب مشتریان. | تهیه طرح‌های اولیه، نقشه‌های طبقات یا ماکت ویترین‌های پیشنهادی. | انتخاب درون‌مایه، نورپردازی، رنگ یا لوازم صحنه مورد استفاده. | نگهداری، بسته‌بندی و ثبت سوابق موجودی لوازم صحنه، محصولات یا اقلام نمایشی. | سرپرستی یا آموزش کارکنان در وظایف روزانه، مانند چیدمان بصری کالا. | عکاسی از ویترین‌ها یا تابلوها. | استفاده از رایانه برای تولید تابلو و علائم.</t>
         </is>
       </c>
     </row>
@@ -892,42 +892,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Set and Exhibit Designers (طراحان صحنه و نمایشگاه)</t>
+          <t>طراحان صحنه و نمایشگاه (Set and Exhibit Designers)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Designer | Display Coordinator | Exhibit Coordinator | Exhibit Designer | Exhibit Preparator | Historical Society Window Dresser | Installations Designer | Projection Designer | Scenic Designer | Set Designer</t>
+          <t>طراح | هماهنگ‌کننده ویترین | هماهنگ‌کننده نمایشگاه | طراح نمایشگاه | آماده‌ساز آثار نمایشگاهی | ویترین‌آرای انجمن تاریخی | طراح چیدمان‌های هنری | طراح نمایش تصویری | طراح صحنه | طراح صحنه</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Act-3D Quest3D | Adobe Acrobat | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Director | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | AutoDesSys form Z | Autodesk 3ds Max | Autodesk AutoCAD | Autodesk Maya | Autodesk Revit | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Corel CorelDraw Graphics Suite | Dassault Systemes SolidWorks | Figure 53 QLab | نرم‌افزار گرافیکی | Maxon Cinema 4D | McNeel Rhinoceros 3D | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Nemetschek Vectorworks Spotlight | Oracle Database | Structured query language SQL | Trimble SketchUp Pro | UNIX</t>
+          <t>Act-3D Quest3D | Adobe Acrobat | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Director | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | AutoDesSys form Z | Autodesk 3ds Max | Autodesk AutoCAD | Autodesk Maya | Autodesk Revit | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Corel CorelDraw Graphics Suite | Dassault Systemes SolidWorks | Figure 53 QLab | نرم‌افزار گرافیکی | Maxon Cinema 4D | McNeel Rhinoceros 3D | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Nemetschek Vectorworks Spotlight | Oracle Database | زبان پرس‌وجوی ساختاریافته SQL | Trimble SketchUp Pro | UNIX</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Reading Comprehension | Active Listening | Speaking | Critical Thinking | Writing | Active Learning | Monitoring | Mathematics</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fine Arts | Design | Computers and Electronics | Building and Construction | History and Archeology | English Language | Communications and Media | Production and Processing | Mathematics | Administration and Management</t>
+          <t>هنرهای زیبا | طراحی | رایانه و الکترونیک | ساختمان و ساخت‌وساز | تاریخ و باستان‌شناسی | زبان انگلیسی | ارتباطات و رسانه | تولید و فرآوری | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fluency of Ideas | Oral Comprehension | Visualization | Written Comprehension | Originality | Problem Sensitivity | Written Expression | Information Ordering | Near Vision | Speech Recognition | Oral Expression | Deductive Reasoning | Speech Clarity | Category Flexibility | Inductive Reasoning | Far Vision | Selective Attention | Flexibility of Closure</t>
+          <t>روانی ایده‌ها | درک شفاهی | تجسم | درک کتبی | اصالت | حساسیت به مسئله | بیان کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | بیان شفاهی | استدلال قیاسی | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>E-Mail | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Freedom to Make Decisions | Time Pressure | Determine Tasks, Priorities and Goals | Contact With Others | Importance of Being Exact or Accurate | Level of Competition | Indoors, Environmentally Controlled | Spend Time Sitting | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls</t>
+          <t>ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | آزادی در تصمیم‌گیری | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | اهمیت دقیق یا درست بودن | سطح رقابت | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Architects, Except Landscape and Naval | Architectural and Civil Drafters | Architecture Teachers, Postsecondary | Art Directors | Commercial and Industrial Designers | Costume Attendants | Craft Artists | Curators | Fabric and Apparel Patternmakers | Fashion Designers | Fine Artists, Including Painters, Sculptors, and Illustrators | Graphic Designers | Interior Designers | Landscape Architects | Layout Workers, Metal and Plastic | Merchandise Displayers and Window Trimmers | Model Makers, Wood | Museum Technicians and Conservators | Special Effects Artists and Animators | Video Game Designers</t>
+          <t>معماران، به‌جز منظر و دریایی | نقشه‌کشان معماری و عمران | مدرسان معماری، پس از متوسطه | مدیران هنری | طراحان تجاری و صنعتی | متصدیان لباس | هنرمندان صنایع دستی | موزه‌داران | الگوسازان پارچه و پوشاک | طراحان مد | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | طراحان داخلی | معماران منظر | کارگران شابلون‌زنی، فلز و پلاستیک | چیدمان‌کنندگان کالا و تزئین‌کنندگان ویترین | مدل‌سازان چوب | تکنسین‌ها و محافظان موزه | هنرمندان جلوه‌های ویژه و انیماتورها | طراحان بازی‌های ویدئویی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Acquire, or arrange for acquisition of, specimens or graphics required to complete exhibits. | Arrange for outside contractors to construct exhibit structures. | Assign staff to complete design ideas and prepare sketches, illustrations, and detailed drawings of sets, or graphics and animation. | Attend rehearsals and production meetings to obtain and share information related to sets. | Collaborate with those in charge of lighting and sound so that those production aspects can be coordinated with set designs or exhibit layouts. | Confer with clients and staff to gather information about exhibit space, proposed themes and content, timelines, budgets, materials, or promotion requirements. | Confer with conservators to determine how to handle an exhibit's environmental aspects, such as lighting, temperature, and humidity, so that objects will be protected and exhibits will be enhanced. | Coordinate the removal of sets, props, and exhibits after productions or events are complete. | Coordinate the transportation of sets that are built off-site, and coordinate their setup at the site of use. | Design and build scale models of set designs, or miniature sets used in filming backgrounds or special effects. | Design and produce displays and materials that can be used to decorate windows, interior displays, or event locations, such as streets and fairgrounds. | Develop set designs, based on evaluation of scripts, budgets, research information, and available locations. | Direct and coordinate construction, erection, or decoration activities to ensure that sets or exhibits meet design, budget, and schedule requirements. | Estimate set- or exhibit-related costs, including materials, construction, and rental of props or locations. | Examine objects to be included in exhibits to plan where and how to display them. | Incorporate security systems into exhibit layouts. | Inspect installed exhibits for conformance to specifications and satisfactory operation of special-effects components. | Observe sets during rehearsals in order to ensure that set elements do not interfere with performance aspects such as cast movement and camera angles. | Plan for location-specific issues, such as space limitations, traffic flow patterns, and safety concerns. | Prepare preliminary renderings of proposed exhibits, including detailed construction, layout, and material specifications, and diagrams relating to aspects such as special effects or lighting. | Prepare rough drafts and scale working drawings of sets, including floor plans, scenery, and properties to be constructed. | Provide supportive materials for exhibits and displays, such as press kits, advertising, publicity notices, posters, brochures, catalogues, and invitations. | Read scripts to determine location, set, and design requirements. | Research architectural and stylistic elements appropriate to the time period to be depicted, consulting experts for information, as necessary. | Select and purchase lumber and hardware necessary for set construction. | Select set props, such as furniture, pictures, lamps, and rugs. | Submit plans for approval, and adapt plans to serve intended purposes, or to conform to budget or fabrication restrictions.</t>
+          <t>تهیه نمونه‌ها یا آثار گرافیکی مورد نیاز برای تکمیل نمایشگاه، یا ترتیب دادن تهیه آن‌ها. | ترتیب دادن قرارداد با پیمانکاران بیرونی برای ساخت سازه‌های نمایشگاهی. | واگذاری وظایف به کارکنان برای تکمیل ایده‌های طراحی و تهیه طرح‌های اولیه، تصویرسازی و نقشه‌های تفصیلی صحنه، یا گرافیک و پویانمایی. | حضور در تمرین‌ها و جلسات تولید برای دریافت و انتقال اطلاعات مرتبط با صحنه. | همکاری با مسئولان نور و صدا تا این جنبه‌های تولید با طراحی صحنه یا چیدمان نمایشگاه هماهنگ شود. | رایزنی با کارفرمایان و کارکنان برای گردآوری اطلاعات درباره فضای نمایشگاه، درون‌مایه و محتوای پیشنهادی، زمان‌بندی، بودجه، مواد یا الزامات تبلیغاتی. | رایزنی با مرمتگران برای تعیین شیوه مدیریت جنبه‌های محیطی نمایشگاه، مانند نور، دما و رطوبت، تا اشیا محافظت شوند و نمایشگاه ارتقا یابد. | هماهنگی برچیدن صحنه‌ها، لوازم صحنه و نمایشگاه‌ها پس از پایان تولید یا رویداد. | هماهنگی حمل صحنه‌هایی که خارج از محل ساخته شده‌اند و هماهنگی برپایی آن‌ها در محل استفاده. | طراحی و ساخت ماکت مقیاس‌دار طرح‌های صحنه، یا صحنه‌های کوچک‌مقیاس مورد استفاده در فیلم‌برداری پس‌زمینه یا جلوه‌های ویژه. | طراحی و تولید ویترین‌ها و موادی که برای تزئین ویترین، چیدمان داخلی یا محل برگزاری رویداد، مانند خیابان‌ها و محوطه‌های نمایشگاهی، به کار می‌روند. | تدوین طرح‌های صحنه، بر پایه ارزیابی فیلم‌نامه، بودجه، اطلاعات پژوهشی و لوکیشن‌های در دسترس. | هدایت و هماهنگی فعالیت‌های ساخت، برپایی یا تزئین برای اطمینان از انطباق صحنه‌ها یا نمایشگاه‌ها با الزامات طراحی، بودجه و زمان‌بندی. | برآورد هزینه‌های مرتبط با صحنه یا نمایشگاه، شامل مواد، ساخت و اجاره لوازم صحنه یا لوکیشن. | بررسی اشیایی که قرار است در نمایشگاه قرار گیرند برای برنامه‌ریزی محل و شیوه نمایش آن‌ها. | گنجاندن سامانه‌های امنیتی در چیدمان نمایشگاه. | بازرسی نمایشگاه‌های برپاشده از نظر انطباق با مشخصات و عملکرد رضایت‌بخش اجزای جلوه‌های ویژه. | مشاهده صحنه‌ها در حین تمرین برای اطمینان از اینکه عناصر صحنه با جنبه‌های اجرایی مانند حرکت بازیگران و زوایای دوربین تداخل ندارند. | برنامه‌ریزی برای مسائل خاص هر مکان، مانند محدودیت فضا، الگوهای رفت‌وآمد و ملاحظات ایمنی. | تهیه پرداخت‌های اولیه نمایشگاه‌های پیشنهادی، شامل مشخصات تفصیلی ساخت، چیدمان و مواد، و نمودارهای مرتبط با جنبه‌هایی مانند جلوه‌های ویژه یا نورپردازی. | تهیه پیش‌نویس‌های اولیه و نقشه‌های اجرایی مقیاس‌دار صحنه، شامل نقشه طبقات، دکور و لوازم صحنه‌ای که باید ساخته شوند. | تهیه مواد پشتیبان برای نمایشگاه‌ها و ویترین‌ها، مانند بسته‌های خبری، تبلیغات، اطلاعیه‌های رسانه‌ای، پوستر، بروشور، کاتالوگ و کارت دعوت. | مطالعه فیلم‌نامه برای تعیین الزامات لوکیشن، صحنه و طراحی. | پژوهش درباره عناصر معماری و سبکی متناسب با دوره تاریخی مورد نظر، و رایزنی با کارشناسان برای کسب اطلاعات در صورت لزوم. | انتخاب و خرید چوب و یراق‌آلات لازم برای ساخت صحنه. | انتخاب لوازم صحنه، مانند مبلمان، تابلو، چراغ و فرش. | ارائه نقشه‌ها برای تأیید و تطبیق آن‌ها با اهداف مورد نظر یا با محدودیت‌های بودجه‌ای و ساخت.</t>
         </is>
       </c>
     </row>
@@ -949,42 +949,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Designers, All Other (طراحان، سایر)</t>
+          <t>طراحان، سایر (Designers, All Other)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Design Consultant | Designer | Environmental Designer | Exhibit Designer | Jewelry Designer | Lighting Designer | Package Designer | Product Designer | Textile Designer | Toy Designer</t>
+          <t>مشاور طراحی | طراح | طراح محیط | طراح نمایشگاه | طراح جواهر | طراح نورپردازی | طراح بسته‌بندی | طراح محصول | طراح منسوجات | طراح اسباب‌بازی</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Adobe Photoshop | Adobe Illustrator | Adobe InDesign | Adobe Acrobat | نرم‌افزار گرافیکی | Microsoft Word | Microsoft Excel | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | Microsoft PowerPoint | نرم‌افزار ویرایش گرافیکی | نرم‌افزار Microsoft Office | Autodesk AutoCAD | نرم‌افزار طراحی به کمک کامپیوتر CAD سه‌بعدی</t>
+          <t>Adobe Photoshop | Adobe Illustrator | Adobe InDesign | Adobe Acrobat | نرم‌افزار گرافیکی | Microsoft Word | Microsoft Excel | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | Microsoft PowerPoint | نرم‌افزار ویرایش گرافیکی | نرم‌افزار Microsoft Office | Autodesk AutoCAD | نرم‌افزار طراحی سه بعدی به کمک کامپیوتر CAD</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Reading Comprehension | Critical Thinking | Active Listening | Speaking | Writing | Monitoring | Active Learning | Learning Strategies</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Design | Fine Arts | English Language | Computers and Electronics | Sales and Marketing | Production and Processing | Communications and Media | Engineering and Technology | Administration and Management</t>
+          <t>طراحی | هنرهای زیبا | زبان انگلیسی | رایانه و الکترونیک | فروش و بازاریابی | تولید و فرآوری | ارتباطات و رسانه | مهندسی و فناوری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization | Visual Color Discrimination | Finger Dexterity</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | تشخیص رنگ بصری | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Face-to-Face Discussions with Individuals and Within Teams | E-Mail | Telephone Conversations | Indoors, Environmentally Controlled | Contact With Others | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Time Pressure | Level of Competition | Work With or Contribute to a Work Group or Team | Spend Time Sitting | Importance of Being Exact or Accurate | Deal With External Customers or the Public in General | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | سطح رقابت | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Commercial and Industrial Designers | Graphic Designers | Interior Designers | Fashion Designers | Set and Exhibit Designers | Floral Designers | Merchandise Displayers and Window Trimmers | Art Directors | Special Effects Artists and Animators | Fine Artists, Including Painters, Sculptors, and Illustrators | Craft Artists | Artists and Related Workers, All Other | Web and Digital Interface Designers | Architects, Except Landscape and Naval | Landscape Architects | Art, Drama, and Music Teachers, Postsecondary | Mechanical Drafters | Video Game Designers | Photographers | Producers and Directors</t>
+          <t>طراحان تجاری و صنعتی | طراحان گرافیک | طراحان داخلی | طراحان مد | طراحان صحنه و نمایشگاه | طراحان گل | چیدمان‌کنندگان کالا و تزئین‌کنندگان ویترین | مدیران هنری | هنرمندان جلوه‌های ویژه و انیماتورها | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | هنرمندان صنایع دستی | هنرمندان و کارکنان مرتبط، سایر | طراحان رابط دیجیتال و وب | معماران، به‌جز منظر و دریایی | معماران منظر | مدرسان هنر، نمایش و موسیقی، آموزش عالی | نقشه‌کشان مکانیک | طراحان بازی‌های ویدئویی | عکاسان | تهیه‌کنندگان و کارگردانان</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Design products, environments, and displays in specialties not classified separately. | Consult with clients to determine design requirements, budgets, and timelines. | Research materials, methods, market trends, and user needs. | Prepare concept sketches, renderings, models, and technical drawings. | Select colors, materials, finishes, and components for designs. | Build prototypes and mock-ups to evaluate appearance and function. | Present design proposals to clients and revise based on feedback. | Coordinate with manufacturers, fabricators, and suppliers during production. | Prepare specifications, cost estimates, and production documentation. | Inspect completed work to verify conformance to design intent and quality standards. | Ensure designs comply with safety, accessibility, and regulatory requirements. | Maintain design files, material samples, and supplier records. | Track project schedules and budgets through completion. | Develop portfolios and promotional materials to attract clients.</t>
+          <t>طراحی محصولات، فضاها و ویترین‌ها در تخصص‌هایی که جداگانه طبقه‌بندی نشده‌اند. | رایزنی با کارفرمایان برای تعیین الزامات طراحی، بودجه و زمان‌بندی. | پژوهش درباره مواد، روش‌ها، روندهای بازار و نیازهای کاربر. | تهیه طرح‌های اولیه ایده، پرداخت‌ها، ماکت‌ها و نقشه‌های فنی. | انتخاب رنگ، مواد، پرداخت‌ها و اجزای طرح. | ساخت نمونه اولیه و ماکت برای ارزیابی ظاهر و کارکرد. | ارائه پیشنهادهای طراحی به کارفرمایان و بازنگری آن‌ها بر پایه بازخورد. | هماهنگی با سازندگان، کارگاه‌ها و تأمین‌کنندگان در جریان تولید. | تهیه مشخصات، برآورد هزینه و مستندات تولید. | بازرسی کار تکمیل‌شده برای راستی‌آزمایی انطباق با هدف طراحی و استانداردهای کیفیت. | حصول اطمینان از انطباق طرح‌ها با الزامات ایمنی، دسترس‌پذیری و مقررات. | نگهداری پرونده‌های طراحی، نمونه مواد و سوابق تأمین‌کنندگان. | پیگیری زمان‌بندی و بودجه پروژه تا تکمیل آن. | تهیه نمونه‌کار و مواد تبلیغاتی برای جذب مشتری.</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Actors (بازیگران)</t>
+          <t>بازیگران (Actors)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Actor | Actress | Comedian | Comic | Community Theater Actor | Ensemble Member | Narrator | Performer | Tour Actor | Voice-Over Artist</t>
+          <t>بازیگر | بازیگر زن | کمدین | کمدین | بازیگر تئاتر محلی | عضو گروه اجرایی | راوی | مجری | بازیگر گروه نمایش سیار | هنرمند صداپیشه</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Reading Comprehension | Speaking | Active Listening | Monitoring | Critical Thinking</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fine Arts | English Language | Communications and Media | Sociology and Anthropology | Psychology | Customer and Personal Service</t>
+          <t>هنرهای زیبا | زبان انگلیسی | ارتباطات و رسانه | جامعه‌شناسی و انسان‌شناسی | روان‌شناسی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Oral Expression | Oral Comprehension | Written Comprehension | Memorization | Speech Clarity | Originality | Near Vision | Problem Sensitivity | Selective Attention | Fluency of Ideas | Speech Recognition</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حفظ کردن | وضوح گفتار | اصالت | بینایی نزدیک | حساسیت به مسئله | توجه انتخابی | روانی ایده‌ها | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Work With or Contribute to a Work Group or Team | Physical Proximity | Contact With Others | E-Mail | Time Pressure | Indoors, Environmentally Controlled | Public Speaking | Face-to-Face Discussions with Individuals and Within Teams | Level of Competition | Importance of Being Exact or Accurate | Spend Time Standing | Telephone Conversations | Deal With External Customers or the Public in General | Frequency of Decision Making</t>
+          <t>کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | ارتباط با دیگران | ایمیل | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | سخنرانی عمومی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سطح رقابت | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Agents and Business Managers of Artists, Performers, and Athletes | Art Directors | Art, Drama, and Music Teachers, Postsecondary | Broadcast Announcers and Radio Disc Jockeys | Choreographers | Costume Attendants | Dancers | Film and Video Editors | Fine Artists, Including Painters, Sculptors, and Illustrators | Makeup Artists, Theatrical and Performance | Models | Music Directors and Composers | Musicians and Singers | News Analysts, Reporters, and Journalists | Poets, Lyricists and Creative Writers | Producers and Directors | Self-Enrichment Teachers | Special Effects Artists and Animators | Talent Directors | Writers and Authors</t>
+          <t>نمایندگان و مدیران تجاری هنرمندان، اجراکنندگان و ورزشکاران | مدیران هنری | مدرسان هنر، نمایش و موسیقی، آموزش عالی | گویندگان رادیو و تلویزیون و دی‌جی‌های رادیو | طراحان رقص | متصدیان لباس | رقصندگان | تدوینگران فیلم و ویدئو | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | میکاپ آرتیست‌های تئاتر و نمایش | مدل‌ها | مدیران موسیقی و آهنگسازان | نوازندگان و خوانندگان | تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | معلمان خودسازی | هنرمندان جلوه‌های ویژه و انیماتورها | مدیران استعداد | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Attend auditions and casting calls to audition for roles. | Collaborate with other actors as part of an ensemble. | Construct puppets and ventriloquist dummies, and sew accessory clothing, using hand tools and machines. | Dress in comical clown costumes and makeup, and perform comedy routines to entertain audiences. | Introduce performances and performers to stimulate excitement and coordinate smooth transition of acts during events. | Learn about characters in scripts and their relationships to each other to develop role interpretations. | Perform humorous and serious interpretations of emotions, actions, and situations, using body movements, facial expressions, and gestures. | Perform original and stock tricks of illusion to entertain and mystify audiences, occasionally including audience members as participants. | Portray and interpret roles, using speech, gestures, and body movements, to entertain, inform, or instruct radio, film, television, or live audiences. | Prepare and perform action stunts for motion picture, television, or stage productions. | Promote productions using means such as interviews about plays or movies. | Read from scripts or books to narrate action or to inform or entertain audiences, utilizing few or no stage props. | Sing or dance during dramatic or comedic performances. | Study and rehearse roles from scripts to interpret, learn and memorize lines, stunts, and cues as directed. | Tell jokes, perform comic dances, songs and skits, impersonate mannerisms and voices of others, contort face, and use other devices to amuse audiences. | Work closely with directors, other actors, and playwrights to find the interpretation most suited to the role. | Work with other crew members responsible for lighting, costumes, make-up, and props. | Write original or adapted material for dramas, comedies, puppet shows, narration, or other performances.</t>
+          <t>شرکت در آزمون بازیگری و فراخوان انتخاب بازیگر برای دریافت نقش. | همکاری با سایر بازیگران به‌عنوان بخشی از یک گروه اجرایی. | ساخت عروسک و آدمک شکم‌گویی و دوخت لباس‌های جانبی، با ابزارهای دستی و ماشین. | پوشیدن لباس و گریم دلقک و اجرای برنامه‌های کمدی برای سرگرمی تماشاگران. | معرفی اجراها و اجراکنندگان برای برانگیختن شور و هماهنگی گذار روان میان بخش‌های برنامه در رویدادها. | شناخت شخصیت‌های فیلم‌نامه و روابط آنان با یکدیگر برای پرورش برداشت از نقش. | اجرای برداشت‌های طنزآمیز و جدی از احساسات، کنش‌ها و موقعیت‌ها، با استفاده از حرکات بدن، حالات چهره و اشاره. | اجرای شعبده‌های اصیل و متداول برای سرگرم و شگفت‌زده کردن تماشاگران، گاه با مشارکت دادن خود آنان. | ایفا و تفسیر نقش، با استفاده از گفتار، اشاره و حرکات بدن، برای سرگرمی، آگاهی‌بخشی یا آموزش مخاطبان رادیو، سینما، تلویزیون یا اجرای زنده. | آماده‌سازی و اجرای بدل‌کاری برای تولیدات سینمایی، تلویزیونی یا صحنه‌ای. | تبلیغ تولیدات از راه‌هایی مانند مصاحبه درباره نمایش‌ها یا فیلم‌ها. | خواندن از روی فیلم‌نامه یا کتاب برای روایت کنش یا آگاهی‌بخشی و سرگرمی مخاطبان، با استفاده از لوازم صحنه اندک یا بدون آن. | خواندن یا رقصیدن در اجراهای نمایشی یا کمدی. | مطالعه و تمرین نقش از روی فیلم‌نامه برای تفسیر، یادگیری و از بر کردن دیالوگ‌ها، بدل‌کاری‌ها و نشانه‌های صحنه، مطابق دستور کارگردان. | لطیفه‌گویی، اجرای رقص و آواز و نمایش کوتاه کمدی، تقلید رفتار و صدای دیگران، تغییر حالت چهره و به‌کارگیری شگردهای دیگر برای سرگرم کردن تماشاگران. | همکاری نزدیک با کارگردانان، سایر بازیگران و نمایشنامه‌نویسان برای یافتن مناسب‌ترین تفسیر از نقش. | همکاری با سایر عوامل مسئول نور، لباس، گریم و لوازم صحنه. | نگارش متن اصیل یا اقتباسی برای نمایش‌های جدی، کمدی، عروسکی، روایت یا سایر اجراها.</t>
         </is>
       </c>
     </row>

--- a/data_extactor/batch_10_fa/batch_0038_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0038_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>هنرهای زیبا | طراحی | زبان انگلیسی | ارتباطات و رسانه | رایانه و الکترونیک | فروش و بازاریابی | تاریخ و باستان‌شناسی | مدیریت و امور اداری</t>
+          <t>هنرهای زیبا | طراحی | زبان انگلیسی | ارتباطات و رسانه | رایانه و الکترونیک | فروش و بازاریابی | تاریخ و باستان‌شناسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | تسهیم زمان | چابکی انگشتان | چابکی دستی | دید دور | حفظ کردن | روانی ایده‌ها | اصالت و ابتکار | تجسم فضایی | ثبات دست و بازو | تشخیص رنگ دیداری</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | اصالت | تجسم | ثبات دست و بازو | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>هنرمندان هنرهای تجسمی از جمله نقاشان، مجسمه‌سازان و تصویرگران | هنرمندان صنایع دستی | هنرمندان جلوه‌های ویژه و پویانماها | مدیران هنری | طراحان گرافیک | طراحان تجاری و صنعتی | طراحان مد و لباس | طراحان داخلی | طراحان صحنه و نمایشگاه | طراحان گل و گل‌آراها | طراحان دکوراسیون و ویترین مغازه | سایر طراحان | عکاسان | تدوینگران فیلم و ویدئو | فیلم‌برداران تلویزیون، ویدئو و سینما | مدرسان هنر، تئاتر و موسیقی در آموزش عالی | کارشناسان فنی و مرمت‌کاران موزه | موزه‌داران | مدرسان دوره‌های آزاد و توسعهٔ فردی | تهیه‌کنندگان و کارگردانان</t>
+          <t>هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | هنرمندان صنایع دستی | پویانماها و طراحان جلوه‌های ویژه | مدیران هنری | طراحان گرافیک | طراحان تجاری و صنعتی | طراحان مد و پوشاک | طراحان داخلی | طراحان صحنه و نمایشگاه | طراحان گل و گل‌آراها | طراحان دکوراسیون و ویترین مغازه | سایر طراحان | عکاسان | تدوین‌گران فیلم و ویدیو | تصویربرداران تلویزیون، ویدیو و سینما | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌ها و مرمت‌گران موزه | موزه‌داران | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | تهیه‌کنندگان و کارگردانان</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>خلق آثار هنری اصیل در قالب رسانه‌ها و تخصص‌های هنری متفرقه | ایده‌پردازی، طراحی اولیه و ساخت نمونه‌های آزمایشی آثار هنری | انتخاب و آماده‌سازی مواد، ابزارها و تکنیک‌های متناسب با نوع اثر | اجرای اثر هنری نهایی با استفاده از روش‌های دستی یا ابزارهای دیجیتال | مذاکره و تبادل نظر با کارفرمایان، گالری‌داران و نمایندگان هنری درباره سفارش‌ها | برآورد مواد اولیه، زمان‌بندی و هزینه‌های اجرایی پروژه‌های سفارشی | عکاسی و مستندسازی آثار نهایی جهت درج در کارنما (پورتفولیو) و کاتالوگ‌ها | بازاریابی و فروش آثار از طریق برگزاری نمایشگاه‌ها، گالری‌ها و بسترهای آنلاین | نگهداری و سازماندهی فضای کارگاهی، تجهیزات و موجودی مواد اولیه | آماده‌سازی، قاب‌گیری، بسته‌بندی و ارسال آثار هنری به خریداران و نمایشگاه‌ها</t>
+          <t>خلق آثار هنری اصیل در رسانه‌ها و تخصص‌هایی که جداگانه طبقه‌بندی نشده‌اند. | تدوین ایده‌ها، طرح‌های اولیه و نمونه‌های آزمایشی آثار هنری. | انتخاب و آماده‌سازی مواد، ابزارها و فنون متناسب با رسانه هنری. | اجرای آثار نهایی با روش‌های دستی و دیجیتال. | رایزنی با کارفرمایان، نگارخانه‌ها و نمایندگان درباره سفارش‌ها و الزامات آن‌ها. | برآورد مواد، زمان و هزینه پروژه‌های سفارشی. | عکاسی و مستندسازی آثار تکمیل‌شده برای نمونه‌کارها و کاتالوگ‌ها. | بازاریابی و فروش آثار از راه نمایشگاه‌ها، نگارخانه‌ها و بسترهای برخط. | نگهداری فضای کارگاه، تجهیزات و موجودی مواد. | قاب‌بندی، نصب، بسته‌بندی و ارسال آثار هنری به مشتریان و محل‌های نمایش. | مطالعه تاریخ هنر، روندها و فنون برای پرورش شیوه هنری. | تهیه پیشنهادها و درخواست‌ها برای دریافت اعتبار، اقامت هنری و سفارش‌های عمومی. | برگزاری کارگاه آموزشی و نمایش عملی فنون برای هنرجویان و عموم مردم. | مرمت، حفاظت یا بازآفرینی آثار موجود در صورت دریافت سفارش.</t>
         </is>
       </c>
     </row>
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>طراحی | مهندسی و فناوری | تولید و فرآوری | مکانیک | رایانه و الکترونیک | ریاضیات | زبان انگلیسی | فیزیک | فروش و بازاریابی | امور اداری و دفتری</t>
+          <t>طراحی | مهندسی و فناوری | تولید و فرآوری | مکانیک | رایانه و الکترونیک | ریاضیات | زبان انگلیسی | فیزیک | فروش و بازاریابی | اداری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>روانی ایده‌ها | اصالت و ابتکار | دید نزدیک | استدلال قیاسی | تجسم فضایی | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | تشخیص رنگ دیداری | توجه انتخابی | انعطاف‌پذیری در ادراک الگوها | انعطاف‌پذیری در طبقه‌بندی | بیان کتبی | دید دور</t>
+          <t>روانی ایده‌ها | اصالت | بینایی نزدیک | استدلال قیاسی | تجسم | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | تشخیص رنگ بصری | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | بیان کتبی | بینایی دور</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>هنرمندان صنایع دستی | تکنسین‌ها و کارشناسان فنی مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | الگوپردازان پارچه و پوشاک | طراحان مد و لباس | تکنسین‌ها و کارشناسان فنی مهندسی صنایع | مهندسان صنایع | طراحان داخلی | چیدمان‌کاران فلز و پلاستیک | مهندسان تولید | مهندسان مواد | دانشمندان مواد | نقشه‌کشان مکانیک | تکنسین‌ها و کارشناسان فنی مهندسی مکانیک | مهندسان مکانیک | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | قالب‌ریزان و شکل‌دهندگان به‌جز فلز و پلاستیک | الگوسازان فلز و پلاستیک | الگوسازان چوب</t>
+          <t>هنرمندان صنایع دستی | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | الگوسازان پارچه و پوشاک | طراحان مد و پوشاک | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | طراحان داخلی | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | مهندسان تولید و ساخت | مهندسان متالورژی و مواد | کارشناسان و دانشمندان علوم مواد | نقشه‌کشان مکانیک | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | الگوسازان فلز و پلاستیک | الگوسازان چوب</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>بررسی و تعیین مشخصات ظاهری، کارکردی و ارگونومیک خطوط تولید محصول | هماهنگی و همفکری با واحدهای مهندسی، بازاریابی، تولید و فروش در خصوص مفاهیم طراحی | ارزیابی امکان‌پذیری طرح‌ها از نظر ایمنی، کارایی، هزینه‌های ساخت و بازخورد بازار | تهیه طرح‌های اولیه، نقشه‌های اجرایی دقیق و مستندات فنی با نرم‌افزارهای CAD | ساخت نمونه‌های اولیه (پروتوتایپ) با متریال‌های مختلف برای ارزیابی عملکردی | اصلاح و بازنگری طرح‌ها بر اساس آزمون‌های فنی، محدودیت‌های تولید و بازخورد مشتریان | ارائه طرح‌ها و گزارش‌های فنی به مدیران و کارفرمایان جهت اخذ تاییدیه نهایی | تحقیق در زمینه ویژگی‌های کیفی، استانداردهای ایمنی، مواد اولیه و روش‌های نوین تولید | تعیین مشخصات بسته‌بندی، گرافیک محصول و راهنماهای کاربری | نظارت بر روند ساخت نمونه‌ها و پیاده‌سازی طرح‌ها در خطوط تولید کارخانه‌ها</t>
+          <t>ارائه مشاوره به شرکت‌ها در موضوعات مربوط به پروژه‌ها یا مسائل هویت بصری سازمان. | رایزنی با واحدهای مهندسی، بازاریابی، تولید یا فروش، یا با مشتریان، برای تعیین و ارزیابی ایده‌های طراحی محصولات تولیدی. | هماهنگ‌سازی ظاهر و کارکرد خطوط محصول. | طراحی مواد گرافیکی برای استفاده به‌عنوان تزئین، تصویرسازی یا تبلیغات روی کالاهای تولیدی و بسته‌بندی یا ظروف. | تدوین استانداردهای صنعتی و دستورالعمل‌های نظارتی. | تدوین رویه‌های تولید و پایش ساخت طرح‌های خود در کارخانه برای بهبود عملیات و کیفیت محصول. | هدایت و هماهنگی ساخت مدل‌ها یا نمونه‌ها و تهیه نقشه‌های اجرایی و برگه‌های مشخصات از روی طرح‌های اولیه. | ارزیابی امکان‌پذیری ایده‌های طراحی، بر پایه عواملی مانند ظاهر، ایمنی، کارکرد، قابلیت تعمیر، بودجه، هزینه‌ها و روش‌های تولید، و ویژگی‌های بازار. | ساخت مدل یا نمونه از کاغذ، چوب، شیشه، پارچه، پلاستیک، فلز یا سایر مواد، با ابزارهای دستی یا برقی. | بررسی ویژگی‌های محصول مانند ایمنی و کیفیت جابه‌جایی آن، جذابیت بازاری، کارایی تولید، و شیوه‌های توزیع، استفاده و نگهداری آن. | اصلاح و پالایش طرح‌ها با استفاده از مدل‌های اجرایی، برای انطباق با مشخصات مشتری، محدودیت‌های تولید یا تغییر روندهای طراحی. | مشارکت در برنامه‌ریزی محصول جدید یا پژوهش بازار، از جمله بررسی نیاز بالقوه به محصولات جدید. | تهیه طرح‌های اولیه ایده‌ها، نقشه‌های تفصیلی، تصویرسازی، آثار هنری یا نقشه‌های اجرایی، با استفاده از ابزارهای نقشه‌کشی، رنگ و قلم‌مو یا تجهیزات طراحی به کمک رایانه. | ارائه طرح‌ها و گزارش‌ها به مشتریان یا کمیته‌های طراحی برای تأیید و گفت‌وگو درباره لزوم اصلاح. | مطالعه نشریات، حضور در نمایشگاه‌ها و بررسی محصولات رقیب و سبک‌ها و نقش‌مایه‌های طراحی برای کسب دید و پرورش ایده‌های طراحی. | پژوهش درباره مشخصات تولید، هزینه‌ها، مواد اولیه و روش‌های ساخت و ارائه برآورد هزینه و فهرست تفصیلی الزامات تولید. | سرپرستی کار دستیاران در سراسر فرایند طراحی.</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | درک مطلب | نظارت | نگارش | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | درک مطلب | نظارت | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>اصالت و ابتکار | درک کتبی | بیان شفاهی | روانی ایده‌ها | تجسم فضایی | دید نزدیک | تشخیص رنگ دیداری | تشخیص گفتار | درک شفاهی | انعطاف‌پذیری در طبقه‌بندی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | مرتب‌سازی اطلاعات | دید دور | توجه انتخابی</t>
+          <t>اصالت | درک کتبی | بیان شفاهی | روانی ایده‌ها | تجسم | بینایی نزدیک | تشخیص رنگ بصری | تشخیص گفتار | درک شفاهی | انعطاف‌پذیری دسته‌بندی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی دور | توجه انتخابی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مدیران هنری | طراحان تجاری و صنعتی | متصدیان لباس صحنه | هنرمندان صنایع دستی | الگوپردازان پارچه و پوشاک | هنرمندان هنرهای تجسمی از جمله نقاشان، مجسمه‌سازان و تصویرگران | طراحان گل و گل‌آراها | طراحان گرافیک | طراحان داخلی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | چهره‌پردازان تئاتر و سینما | طراحان دکوراسیون و ویترین مغازه | کارگران رنگ‌آمیزی، پوشش‌دهی و تزئین | الگوسازان فلز و پلاستیک | فروشندگان خرده‌فروشی | طراحان صحنه و نمایشگاه | دوزندگان دستی | متصدیان چرخ‌های خیاطی | کارگران و تعمیرکاران کفش و چرم | خیاطان زنانه، مردانه و سفارشی‌دوز</t>
+          <t>مدیران هنری | طراحان تجاری و صنعتی | متصدیان و جامه داران لباس صحنه | هنرمندان صنایع دستی | الگوسازان پارچه و پوشاک | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گل و گل‌آراها | طراحان گرافیک | طراحان داخلی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | چهره‌پردازان و گریموران تئاتر و سینما | طراحان دکوراسیون و ویترین مغازه | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | الگوسازان فلز و پلاستیک | فروشندگان خرده‌فروشی | طراحان صحنه و نمایشگاه | دوزندگان دستی | چرخکاران صنعتی | کارگران و تعمیرکاران کفش و چرم | خیاطان و دوزندگان سفارشی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>رصد و تحلیل روندهای جهانی مد، رنگ و پارچه از طریق نشریات و رویدادهای تخصصی | ترسیم طرح‌های اولیه و دستی البسه و اکسسوری به همراه جزئیات فنی و پالت رنگی | انتخاب انواع پارچه، تریم‌ها، یراق‌آلات و تعیین تکنیک‌های دوخت و تولید البسه | طراحی الگوهای پایه، برش قطعات و دوخت نمونه‌های اولیه جهت پرو و آزمون | بررسی، اصلاح و برازش نمونه‌های دوخته‌شده بر روی تن‌پوش یا مانکن | طراحی مجموعه‌های پوشاک سفارشی برای مشتریان خاص، تئاتر، تلویزیون یا سینما | همکاری و هماهنگی با خیاطان، الگوسازان و تکنسین‌های خط تولید در فرآیند دوخت | تعیین بازار هدف و قیمت‌گذاری محصولات متناسب با بودجه و بخش‌بندی بازار | آماده‌سازی شناسنامه فنی محصول و مشخصات مراقبت از پارچه جهت تولید انبوه | تهیه نمونه‌های نمایشی برای ارائه به مدیران فروش، کارفرمایان و رویدادهای معرفی محصول</t>
+          <t>تطبیق ایده‌های سایر طراحان برای بازار انبوه. | حضور در نمایش‌های مد و بررسی مجلات و راهنماهای پوشاک برای گردآوری اطلاعات درباره روندهای مد و ترجیحات مصرف‌کننده. | همکاری با سایر طراحان برای هماهنگی محصولات و طرح‌های ویژه. | رایزنی با مدیران فروش و مدیریت یا با مشتریان برای گفت‌وگو درباره ایده‌های طراحی. | طراحی پوشاک و لوازم جانبی سفارشی برای اشخاص، خرده‌فروشان یا تولیدات تئاتری، تلویزیونی یا سینمایی. | تعیین قیمت برای هر مدل. | تدوین مجموعه‌ای از محصولات یا لوازم جانبی و بازاریابی آن‌ها از راه بسترهایی مانند بوتیک‌ها یا کاتالوگ‌های سفارش پستی. | هدایت و هماهنگی کارکنانی که الگو می‌کشند و برش می‌دهند و نمونه یا پوشاک نهایی را می‌دوزند. | کشیدن الگو برای اقلام طراحی‌شده، برش الگو و برش پارچه مطابق الگو، با استفاده از ابزارهای اندازه‌گیری و قیچی. | بررسی نمونه لباس‌ها روی مدل و بیرون از آن و اصلاح طرح‌ها برای دستیابی به اثر دلخواه. | شناسایی بازارهای هدف طرح‌ها، با در نظر گرفتن عواملی مانند سن، جنسیت و جایگاه اجتماعی‌اقتصادی. | ارائه نمونه لباس به نمایندگان و کارشناسان فروش و ترتیب دادن نمایش نمونه‌ها در جلسات فروش یا نمایش‌های مد. | خرید اقلام پوشاک و لوازم جانبی نو یا دست‌دوم در صورت نیاز برای تکمیل طرح‌ها. | مطالعه فیلم‌نامه و رایزنی با کارگردانان و سایر عوامل تولید برای تدوین ایده‌های طراحی و برنامه‌ریزی تولید. | پژوهش درباره سبک‌ها و دوره‌های تاریخی پوشاک مورد نیاز تولیدات سینمایی یا تئاتری. | انتخاب مواد و فنون تولید مورد استفاده برای محصولات. | دوخت بخش‌های پارچه به یکدیگر برای ساخت ماکت یا نمونه لباس و اقلام، با استفاده از تجهیزات دوخت. | ترسیم طرح‌های اولیه و تفصیلی پوشاک یا لوازم جانبی و نگارش مشخصاتی مانند ترکیب رنگ، شیوه دوخت، نوع پارچه و الزامات لوازم جانبی. | آزمون پارچه‌ها یا نظارت بر آزمون آن‌ها تا برچسب راهنمای نگهداری لباس تهیه شود. | بازدید از نمایشگاه‌های پارچه برای به‌روز ماندن از جدیدترین منسوجات.</t>
         </is>
       </c>
     </row>
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید و فرآوری | فروش و بازاریابی | طراحی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | تولید و فرآوری | فروش و بازاریابی | طراحی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تجسم فضایی | دید نزدیک | تشخیص رنگ دیداری | اصالت و ابتکار | وضوح گفتار | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | مرتب‌سازی اطلاعات | تشخیص گفتار | دید دور | قدرت بالاتنه | چابکی انگشتان | چابکی دستی | ثبات دست و بازو | استدلال قیاسی | توجه انتخابی | درک کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | تجسم | بینایی نزدیک | تشخیص رنگ بصری | اصالت | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | ترتیب‌دهی اطلاعات | تشخیص گفتار | بینایی دور | قدرت تنه | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | استدلال قیاسی | توجه انتخابی | درک کتبی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>طراحان تجاری و صنعتی | هنرمندان صنایع دستی | فروشندگان دوره‌گرد، روزنامه‌فروشان و دستفروشان و مشاغل مرتبط | الگوپردازان پارچه و پوشاک | طراحان مد و لباس | هنرمندان هنرهای تجسمی از جمله نقاشان، مجسمه‌سازان و تصویرگران | آرایشگران، پیرایشگران و متخصصان زیبایی | طراحان داخلی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | طراحان دکوراسیون و ویترین مغازه | بسته‌بندها و کارگران بسته‌بندی دستی | کارگران رنگ‌آمیزی، پوشش‌دهی و تزئین | الگوسازان فلز و پلاستیک | عکاسان | فروشندگان خرده‌فروشی | دوزندگان دستی | متصدیان چرخ‌های خیاطی | کارگران و تعمیرکاران کفش و چرم | انبارداران و متصدیان چیدمان و تحویل کالا | خیاطان زنانه، مردانه و سفارشی‌دوز</t>
+          <t>طراحان تجاری و صنعتی | هنرمندان صنایع دستی | بازاریابان حضوری و فروشندگان خیابانی | الگوسازان پارچه و پوشاک | طراحان مد و پوشاک | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | آرایشگران و متخصصان زیبایی | طراحان داخلی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | طراحان دکوراسیون و ویترین مغازه | کارگران بسته‌بندی دستی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | الگوسازان فلز و پلاستیک | عکاسان | فروشندگان خرده‌فروشی | دوزندگان دستی | چرخکاران صنعتی | کارگران و تعمیرکاران کفش و چرم | متصدیان چیدمان و آماده‌سازی سفارش | خیاطان و دوزندگان سفارشی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>بررسی و دریافت نیازها، ترجیحات، بودجه و زمان‌بندی مشتریان برای انواع سفارش‌ها | طراحی و چیدمان انواع دسته‌گل، سبد گل، پایه‌گل، تاج‌گل و تراریوم | انتخاب گل‌ها، شاخ‌وبرگ‌ها و تزئینات متناسب با فرم، رنگ و ماندگاری طرح | آماده‌سازی، هرس، تغذیه و نگهداری اصولی گل‌ها و گیاهان تازه در انبار و نمایشگاه | گل‌آرایی و اجرای دکوراسیون مجالس، تالارها، جشن‌ها، همایش‌ها و مراسم تشریفاتی | سفارش و خرید گل‌های شاخه‌بریده و اقلام مصرفی از عمده‌فروشان و تولیدکنندگان | بسته‌بندی، تزئین نهایی و قیمت‌گذاری بر روی محصولات آماده تحویل | ارائه مشاوره و راهنمایی به مشتریان در خصوص اصول نگهداری و ماندگاری گیاهان و گل‌ها | چیدمان، دیزاین و به‌روزرسانی ویترین و فضای فروشگاه جهت جذب مشتریان | مدیریت فرآیندهای مالی، صدور فاکتور و پیگیری ارسال دقیق سفارش‌ها به مقصد</t>
+          <t>برگزاری کلاس یا نمایش عملی، یا آموزش سایر کارکنان. | رایزنی با مشتریان درباره قیمت و نوع آرایش گل مورد نظر و تاریخ، زمان و محل تحویل. | ایجاد و تغییر ویترین و چیدمان داخلی فروشگاه، طرح‌ها و ظاهر آن برای ارتقای تصویر مغازه. | تزئین ساختمان‌ها، سالن‌ها، اماکن مذهبی یا سایر مکان‌ها برای مهمانی، مراسم ازدواج و سایر مناسبت‌ها، یا سرپرستی این تزئینات. | تحویل آرایش‌های گل به مشتریان، یا نظارت بر کارکنان مسئول تحویل. | آگاه‌سازی مشتریان درباره مراقبت، نگهداری و جابه‌جایی گل‌ها و شاخ‌وبرگ‌های گوناگون، گیاهان آپارتمانی و سایر اقلام. | سفارش و خرید گل و ملزومات از عمده‌فروشان و پرورش‌دهندگان. | انجام امور عمومی نظافت فروشگاه برای اطمینان از تمیزی و مرتب بودن مغازه. | انجام وظایف اداری و خدمات خرده‌فروشی، مانند نگهداری سوابق مالی، خدمت به مشتریان، پاسخ‌گویی تلفنی، فروش اقلام هدیه و دریافت وجه. | طراحی آرایش گل مطابق خواسته مشتری، با به‌کارگیری دانش طراحی و ویژگی‌های مواد، یا انتخاب الگوی طراحی استاندارد مناسب. | انتخاب گل و شاخ‌وبرگ برای آرایش‌ها، با کار روی ترکیب‌های متعدد برای ساخت و پرورش خلاقیت‌های تازه. | پیرایش مواد و آماده‌سازی دسته‌گل، تاج گل، تراریوم و سایر اقلام، با استفاده از قیچی، قالب، مفتول، سنجاق، چسب گل، فوم و سایر مواد. | بازکردن بسته‌های کالا هنگام ورود به مغازه. | آبیاری گیاهان و برش، آماده‌سازی و تمیز کردن گل و شاخ‌وبرگ برای نگهداری. | بسته‌بندی و قیمت‌گذاری آرایش‌های آماده‌شده.</t>
         </is>
       </c>
     </row>
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | درک مطلب | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | درک مطلب | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>طراحی | رایانه و الکترونیک | هنرهای زیبا | ارتباطات و رسانه | زبان انگلیسی | فروش و بازاریابی | خدمات مشتریان و خدمات فردی | تولید و فرآوری | مدیریت و امور اداری</t>
+          <t>طراحی | رایانه و الکترونیک | هنرهای زیبا | ارتباطات و رسانه | زبان انگلیسی | فروش و بازاریابی | خدمات مشتری و شخصی | تولید و فرآوری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>اصالت و ابتکار | روانی ایده‌ها | دید نزدیک | درک کتبی | درک شفاهی | بیان کتبی | بیان شفاهی | تشخیص رنگ دیداری | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | مرتب‌سازی اطلاعات | استدلال استقرایی | حساسیت به مسئله | تجسم فضایی | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>اصالت | روانی ایده‌ها | بینایی نزدیک | درک کتبی | درک شفاهی | بیان کتبی | بیان شفاهی | تشخیص رنگ بصری | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | تجسم | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدیران هنری | طراحان تجاری و صنعتی | هنرمندان صنایع دستی | صفحه‌آراها و ناشران رومیزی | الگوپردازان پارچه و پوشاک | طراحان مد و لباس | تدوینگران فیلم و ویدئو | هنرمندان هنرهای تجسمی از جمله نقاشان، مجسمه‌سازان و تصویرگران | طراحان داخلی | طراحان دکوراسیون و ویترین مغازه | عکاسان | تکنسین‌ها و کارگران مراحل پیش از چاپ | تهیه‌کنندگان و کارگردانان | طراحان صحنه و نمایشگاه | توسعه‌دهندگان نرم‌افزار | هنرمندان جلوه‌های ویژه و پویانماها | طراحان بازی‌های ویدئویی | توسعه‌دهندگان وب | طراحان وب و رابط کاربری دیجیتال | نویسندگان و پدیدآورندگان</t>
+          <t>مدیران هنری | طراحان تجاری و صنعتی | هنرمندان صنایع دستی | متخصصان نشر رومیزی و صفحه‌آرایی دیجیتال | الگوسازان پارچه و پوشاک | طراحان مد و پوشاک | تدوین‌گران فیلم و ویدیو | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان داخلی | طراحان دکوراسیون و ویترین مغازه | عکاسان | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | تهیه‌کنندگان و کارگردانان | طراحان صحنه و نمایشگاه | توسعه‌دهندگان نرم‌افزار | پویانماها و طراحان جلوه‌های ویژه | طراحان بازی‌های ویدیویی | توسعه‌دهندگان وب | طراحان وب و رابط‌های دیجیتال | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>برگزاری جلسات مشاوره با کارفرمایان و مدیران جهت دریافت بریف و اهداف طراحی | خلق ایده‌ها، طرح‌های مفهومی، اتودهای اولیه و لی‌اوت‌های گرافیکی | انتخاب و هماهنگ‌سازی پالت‌های رنگی، ساختار تایپوگرافی، فونت‌ها و تصاویر | طراحی اقلام گرافیکی نظیر نشان‌واره (لوگو)، هویت بصری برند، بسته‌بندی و پوسترها | آماده‌سازی، بهینه‌سازی و خروجی‌گرفتن از فایل‌های دیجیتال نهایی برای چاپ و نشر دیجیتال | طراحی صفحات، بنرها و گرافیک‌های اختصاصی برای وب‌سایت‌ها و شبکه‌های اجتماعی | نظارت فنی بر فرآیند چاپ و تطابق کیفیت رنگی و ساختاری خروجی با استانداردهای طراحی | مدیریت و سازماندهی آرشیو فایل‌ها، دارایی‌های بصری، تایپ‌فیس‌ها و تصاویر | تعامل و هماهنگی با تیم‌های بازاریابی، تولید محتوا و چاپخانه‌ها | بازنگری و اعمال اصلاحات روی طرح‌ها بر اساس بازخورد مدیران هنری و سفارش‌دهندگان</t>
+          <t>رایزنی با مشتریان برای گفت‌وگو و تعیین طراحی چیدمان. | خلق طرح‌ها، ایده‌ها و نمونه چیدمان‌ها، بر پایه دانش اصول صفحه‌آرایی و مفاهیم زیبایی‌شناختی طراحی. | تعیین اندازه و آرایش مواد تصویری و متن، و انتخاب سبک و اندازه قلم. | تدوین گرافیک و چیدمان برای تصویرسازی محصول، نشان‌های شرکتی و وب‌سایت‌ها. | ترسیم و چاپ چارت‌ها، نمودارها، تصویرسازی‌ها و سایر آثار گرافیکی، با استفاده از رایانه. | وارد کردن اطلاعات در تجهیزات رایانه‌ای برای ساخت چیدمان برای مشتری یا سرپرست. | نگهداری بایگانی تصاویر، عکس‌ها یا آثار پیشین. | علامت‌گذاری، چسباندن و مونتاژ چیدمان‌های نهایی برای آماده‌سازی جهت چاپ. | عکاسی از چیدمان‌ها با دوربین برای تهیه نسخه چاپی چیدمان جهت ارائه به سرپرستان یا مشتریان. | آماده‌سازی فایل‌های دیجیتال برای چاپ. | تهیه تصویرسازی یا طرح‌های اولیه مواد، گفت‌وگو درباره آن‌ها با مشتریان یا سرپرستان و اعمال تغییرات لازم. | تهیه یادداشت‌ها و دستورالعمل برای کارکنانی که چیدمان‌های نهایی را برای چاپ مونتاژ و آماده می‌کنند. | تولید گرافیک ثابت و متحرک برای بخش‌های زنده و ضبط‌شده اخبار تلویزیونی، با استفاده از تجهیزات ویدئویی الکترونیکی. | پژوهش درباره نرم‌افزارها یا مفاهیم طراحی جدید. | پژوهش درباره مخاطب هدف پروژه‌ها. | بازبینی چیدمان‌های نهایی و ارائه پیشنهاد برای بهبود، در صورت نیاز. | مطالعه تصویرسازی‌ها و عکس‌ها برای برنامه‌ریزی نحوه ارائه مواد، محصولات یا خدمات. | استفاده از نرم‌افزارهای رایانه‌ای برای تولید تصاویر جدید. | نگارش یا ویرایش متن برای مشتریان.</t>
         </is>
       </c>
     </row>
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>طراحی | خدمات مشتریان و خدمات فردی | ساختمان و ساخت‌وساز | زبان انگلیسی | فروش و بازاریابی | مدیریت و امور اداری | رایانه و الکترونیک | ایمنی و امنیت عمومی | هنرهای زیبا | امور اداری و دفتری | روان‌شناسی | امور کارکنان و منابع انسانی</t>
+          <t>طراحی | خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | زبان انگلیسی | فروش و بازاریابی | مدیریت و اداره | رایانه و الکترونیک | ایمنی و امنیت عمومی | هنرهای زیبا | اداری | روان‌شناسی | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>روانی ایده‌ها | اصالت و ابتکار | درک شفاهی | بیان شفاهی | تجسم فضایی | دید نزدیک | درک کتبی | حساسیت به مسئله | تشخیص رنگ دیداری | تشخیص گفتار | وضوح گفتار | بیان کتبی | استدلال قیاسی | انعطاف‌پذیری در طبقه‌بندی | استدلال استقرایی | مرتب‌سازی اطلاعات | دید دور | استدلال ریاضی | توجه انتخابی</t>
+          <t>روانی ایده‌ها | اصالت | درک شفاهی | بیان شفاهی | تجسم | بینایی نزدیک | درک کتبی | حساسیت به مسئله | تشخیص رنگ بصری | تشخیص گفتار | وضوح گفتار | بیان کتبی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی دور | استدلال ریاضی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>معماران، به‌جز معماران منظر و سازه‌های دریایی | نقشه‌کشان معماری و عمران | مدیران هنری | نجاران | نصابان موکت و کف‌پوش | طراحان تجاری و صنعتی | هنرمندان صنایع دستی | طراحان مد و لباس | پرداخت‌کاران مبلمان و سازه‌های چوبی | طراحان گرافیک | معماران منظر | چیدمان‌کاران فلز و پلاستیک | تکنسین‌های نور و روشنایی | نقشه‌کشان مکانیک | طراحان دکوراسیون و ویترین مغازه | مدل‌سازان چوب | کارگران رنگ‌آمیزی، پوشش‌دهی و تزئین | گچ‌کاران و سیمان‌کاران | طراحان صحنه و نمایشگاه | کاشی‌کاران و سنگ‌کاران</t>
+          <t>مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | نقشه‌کشان معماری و عمران | مدیران هنری | نجاران و درودگران | موکت‌کاران و نصابان فرش | طراحان تجاری و صنعتی | هنرمندان صنایع دستی | طراحان مد و پوشاک | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | طراحان گرافیک | مهندسان معمار منظر | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | تکنسین‌های نورپردازی | نقشه‌کشان مکانیک | طراحان دکوراسیون و ویترین مغازه | مدل‌سازان چوب | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | سفیدکاران و گچ‌کاران نما | طراحان صحنه و نمایشگاه | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>مشاوره با کارفرمایان جهت شناسایی نیازها، کاربری فضا، سبک مورد نظر و تعیین بودجه | طراحی پلان‌های چیدمان، نقشه‌های اجرایی، سقف کاذب، نورپردازی و تاسیسات داخلی | تهیه مدل‌های سه‌بعدی و رندرهای واقع‌گرایانه با نرم‌افزارهای تخصصی CAD و 3D | انتخاب و پیشنهاد متریال‌ها، پوشش‌های کف و دیوار، مبلمان، روشنایی و اکسسوری‌ها | برآورد مقادیر متریال، تهیه صورت مقادیر و برآورد هزینه‌های اجرایی پروژه | هماهنگی مستمر با معماران، مهندسان تاسیسات، پیمانکاران و مجریان ساختمانی | نظارت میدانی و مستمر بر عملیات اجرایی و تطابق آن با نقشه‌ها و جزئیات طراحی | رعایت ضوابط فنی، مقررات ملی ساختمان، استانداردهای دسترس‌پذیری و ایمنی آتش‌نشانی | تهیه نقشه‌های جزئیات اجرایی (Shop Drawings) برای عناصر سفارشی مانند کابینت و کمدها | مدیریت خرید، تدارکات و نصب نهایی المان‌های دکوراتیو و تجهیزات داخلی</t>
+          <t>ارائه مشاوره به کارفرما درباره عوامل طراحی داخلی، مانند برنامه‌ریزی فضا، چیدمان و استفاده از مبلمان یا تجهیزات، و هماهنگی رنگ. | رایزنی با کارفرما برای تعیین عوامل مؤثر بر برنامه‌ریزی فضاهای داخلی، مانند بودجه، ترجیحات معماری، هدف و کارکرد. | هماهنگی با سایر متخصصان، مانند پیمانکاران، معماران، مهندسان و لوله‌کش‌ها، برای تضمین موفقیت کار. | طراحی نقشه‌ها به‌گونه‌ای که ایمن و منطبق بر الزامات دسترس‌پذیری معلولان (ADA) باشد. | طراحی فضاها به‌شکل سازگار با محیط‌زیست، با استفاده از مواد پایدار و بازیافتی در صورت امکان. | برآورد نیازها و هزینه‌های مواد و ارائه طرح به کارفرما برای تأیید. | تدوین طرح فضا به‌گونه‌ای که کاربردی، زیبا و متناسب با اهداف مورد نظر باشد، مانند افزایش بهره‌وری یا فروش کالا. | بازرسی کار ساخت در محل برای اطمینان از رعایت نقشه‌های طراحی. | برنامه‌ریزی و طراحی فضاهای داخلی قایق، هواپیما، اتوبوس، قطار و سایر فضاهای بسته. | ارائه ایده‌های طراحی در قالب کلاژ یا نقشه. | پژوهش و کاوش درباره استفاده از مواد، فناوری‌ها و محصولات جدید برای به‌کارگیری در طرح‌ها. | پژوهش درباره الزامات آیین‌نامه‌های بهداشت و ایمنی برای پشتیبانی از طراحی. | بازبینی و تهیه جزئیات نقشه‌های کارگاهی برای طرح‌های ساخت. | انتخاب یا طراحی و خرید مبلمان، آثار هنری و لوازم جانبی. | واگذاری ساخت، نصب و چیدمان موکت، تجهیزات ثابت، لوازم جانبی، پرده، رنگ و پوشش دیوار، آثار هنری، مبلمان و اقلام مرتبط به پیمانکاران فرعی. | استفاده از نقشه‌کشی به کمک رایانه (CAD) و نرم‌افزارهای مرتبط برای تولید اسناد اجرایی.</t>
         </is>
       </c>
     </row>
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | فروش و بازاریابی | زبان انگلیسی | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>تجسم فضایی | وضوح گفتار | درک شفاهی | بیان شفاهی | روانی ایده‌ها | تشخیص گفتار | چابکی دستی | انعطاف‌پذیری در طبقه‌بندی | چابکی انگشتان | قدرت بالاتنه | دید نزدیک | دید دور | تشخیص رنگ دیداری | مرتب‌سازی اطلاعات | اصالت و ابتکار | استدلال قیاسی | حساسیت به مسئله | انعطاف‌پذیری کششی بدن | استقامت بدنی | قدرت ایستایی | هماهنگی میان اندام‌ها | ثبات دست و بازو | هماهنگی کلی بدن | استدلال استقرایی | بیان کتبی | درک کتبی</t>
+          <t>تجسم | وضوح گفتار | درک شفاهی | بیان شفاهی | روانی ایده‌ها | تشخیص گفتار | مهارت دستی | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | قدرت تنه | بینایی نزدیک | بینایی دور | تشخیص رنگ بصری | ترتیب‌دهی اطلاعات | اصالت | استدلال قیاسی | حساسیت به مسئله | انعطاف‌پذیری دامنه حرکت | استقامت | قدرت ایستا | هماهنگی چند عضو | ثبات دست و بازو | هماهنگی کلی بدن | استدلال استقرایی | بیان کتبی | درک کتبی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کارشناسان فروش تبلیغات | مدیران تبلیغات و روابط عمومی | مدیران هنری | طراحان تجاری و صنعتی | متصدیان باجه و کارکنان پذیرش و اجاره کالا | هنرمندان صنایع دستی | نمایش‌دهندگان و مروجان کالا | فروشندگان دوره‌گرد، روزنامه‌فروشان و دستفروشان و مشاغل مرتبط | طراحان مد و لباس | سرپرستان رده‌اول فروشندگان خرده‌فروشی | طراحان گل و گل‌آراها | طراحان گرافیک | طراحان داخلی | مدیران بازاریابی | فروشندگان خرده‌فروشی | مدیران فروش | کارشناسان فروش خدمات به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری | طراحان صحنه و نمایشگاه | انبارداران و متصدیان چیدمان و تحویل کالا | خریداران عمده و خرده‌فروشی به‌جز محصولات کشاورزی</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | مدیران تبلیغات و روابط ترویجی | مدیران هنری | طراحان تجاری و صنعتی | متصدیان باجه و کرایه کالا و خدمات | هنرمندان صنایع دستی | معرفی‌کنندگان و مروجان کالا | بازاریابان حضوری و فروشندگان خیابانی | طراحان مد و پوشاک | سرپرستان رده‌اول فروشندگان خرده‌فروشی | طراحان گل و گل‌آراها | طراحان گرافیک | طراحان داخلی | مدیران بازاریابی | فروشندگان خرده‌فروشی | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | طراحان صحنه و نمایشگاه | متصدیان چیدمان و آماده‌سازی سفارش | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ایده‌پردازی و طراحی کانسپت‌های بصری برای ویترین و دکورهای داخل فروشگاه | مونتاژ، نصب و آرایش المان‌های دکوراتیو، استندها، بک‌دراپ‌ها و سازه‌های نمایشی | پوشاندن، استایل‌دهی و چیدمان مانکن‌ها متناسب با سبک و روندهای فصل | چیدمان هدفمند و جذاب محصولات در قفسه‌ها، ویترین‌ها و فضاهای تبلیغاتی | تنظیم زوایای نورپردازی، پالت‌های رنگی و نورهای نقطه‌ای روی کالاها | طراحی، ساخت و نصب تابلوهای راهنما، برچسب‌های قیمت و پوسترهای پروموشن | تغییر دوره‌ای و بازچیدمان دکوراسیون متناسب با کمپین‌های تبلیغاتی و فصول | نگهداری، ترمیم و انبارداری وسایل تزئینی، مانکن‌ها و تجهیزات دکور | تعامل مستمر با مدیران فروشگاه و بازاریابی در خصوص معرفی محصولات کلیدی | آموزش کارکنان فروش در خصوص حفظ نظم چیدمان و هماهنگی رنگی البسه و کالاها</t>
+          <t>چیدمان لوازم صحنه، مبلمان، کالا، پس‌زمینه یا سایر لوازم جانبی، مطابق طرح‌های اولیه آماده‌شده. | مونتاژ یا برپایی ویترین، مبلمان یا محصولات در فضای فروشگاه، با استفاده از رنگ، نور، تصویر یا سایر لوازم جانبی برای نمایش محصول. | شرکت در دوره‌های آموزشی یا جلسات برنامه‌ریزی شرکت برای دریافت ایده‌های تازه جهت معرفی محصولات. | تغییر یا جابه‌جایی ویترین‌ها، فضاهای نمایش داخلی یا تابلوها متناسب با تغییر موجودی یا برنامه‌های ترویجی. | همکاری با دیگران برای تأمین محصولات یا سایر اقلام نمایشی. | ساخت یا مونتاژ ویترین‌ها یا اجزای آن‌ها از پارچه، شیشه، کاغذ یا پلاستیک، با ابزارهای دستی یا ابزارهای برقی نجاری، مطابق مشخصات. | رایزنی با کارکنان تبلیغات یا فروش برای تعیین نوع کالای برجسته‌شده و زمان و مکان هر ویترین. | رایزنی با مدیران فروشگاه، خریداران، همکاران فروش، کارکنان خدمات یا کارکنان فنی برای تعیین محل مناسب ویترین‌ها یا محصولات. | برش طرح‌ها روی مقوا، تخته فشرده یا تخته‌سه‌لایی، مطابق نقش‌مایه رویداد. | تدوین ایده‌ها یا طرح‌های ویترین کالا یا تزئین ویترین. | پوشاندن لباس بر مانکن‌ها برای ویترین. | نصب غرفه، نمایشگاه، ویترین، موکت یا پرده، مطابق نقشه طبقات ساختمان یا مشخصات. | نصب تزئینات، مانند پرچم، بنر، چراغ‌های تزئینی یا پارچه‌آرایی روی ساختمان، خیابان، سالن نمایشگاه یا غرفه یا در داخل آن‌ها. | آموزش کارکنان فروش در زمینه هماهنگی رنگ رگال‌های پوشاک یا ویترین‌های پیشخوان. | نگهداری لوازم صحنه، محصولات یا مانکن‌ها، بازرسی آن‌ها از نظر عیب، ترمیم جزئی، نظافت پس از مراجعه مشتریان یا اعمال پوشش‌های محافظ در صورت نیاز. | دریافت نقشه‌ها از طراحان یا مدیران ویترین و گفت‌وگو درباره اجرای آن‌ها با مشتریان یا سرپرستان. | قرار دادن برچسب قیمت یا تابلوهای توضیحی روی پس‌زمینه، تجهیزات ثابت، کالا یا کف. | طراحی ویترین‌های تجاری برای جلب و جذب مشتریان. | تهیه طرح‌های اولیه، نقشه‌های طبقات یا ماکت ویترین‌های پیشنهادی. | انتخاب درون‌مایه، نورپردازی، رنگ یا لوازم صحنه مورد استفاده. | نگهداری، بسته‌بندی و ثبت سوابق موجودی لوازم صحنه، محصولات یا اقلام نمایشی. | سرپرستی یا آموزش کارکنان در وظایف روزانه، مانند چیدمان بصری کالا. | عکاسی از ویترین‌ها یا تابلوها. | استفاده از رایانه برای تولید تابلو و علائم.</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>هنرهای زیبا | طراحی | رایانه و الکترونیک | ساختمان و ساخت‌وساز | تاریخ و باستان‌شناسی | زبان انگلیسی | ارتباطات و رسانه | تولید و فرآوری | ریاضیات | مدیریت و امور اداری</t>
+          <t>هنرهای زیبا | طراحی | رایانه و الکترونیک | ساختمان و ساخت‌وساز | تاریخ و باستان‌شناسی | زبان انگلیسی | ارتباطات و رسانه | تولید و فرآوری | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>روانی ایده‌ها | درک شفاهی | تجسم فضایی | درک کتبی | اصالت و ابتکار | حساسیت به مسئله | بیان کتبی | مرتب‌سازی اطلاعات | دید نزدیک | تشخیص گفتار | بیان شفاهی | استدلال قیاسی | وضوح گفتار | انعطاف‌پذیری در طبقه‌بندی | استدلال استقرایی | دید دور | توجه انتخابی | انعطاف‌پذیری در ادراک الگوها</t>
+          <t>روانی ایده‌ها | درک شفاهی | تجسم | درک کتبی | اصالت | حساسیت به مسئله | بیان کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | بیان شفاهی | استدلال قیاسی | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>معماران، به‌جز معماران منظر و سازه‌های دریایی | نقشه‌کشان معماری و عمران | مدرسان معماری در آموزش عالی | مدیران هنری | طراحان تجاری و صنعتی | متصدیان لباس صحنه | هنرمندان صنایع دستی | موزه‌داران | الگوپردازان پارچه و پوشاک | طراحان مد و لباس | هنرمندان هنرهای تجسمی از جمله نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | طراحان داخلی | معماران منظر | چیدمان‌کاران فلز و پلاستیک | طراحان دکوراسیون و ویترین مغازه | مدل‌سازان چوب | کارشناسان فنی و مرمت‌کاران موزه | هنرمندان جلوه‌های ویژه و پویانماها | طراحان بازی‌های ویدئویی</t>
+          <t>مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | نقشه‌کشان معماری و عمران | استادان و مدرسان معماری در دانشگاه‌ها و مراکز آموزش عالی | مدیران هنری | طراحان تجاری و صنعتی | متصدیان و جامه داران لباس صحنه | هنرمندان صنایع دستی | موزه‌داران | الگوسازان پارچه و پوشاک | طراحان مد و پوشاک | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | طراحان داخلی | مهندسان معمار منظر | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | طراحان دکوراسیون و ویترین مغازه | مدل‌سازان چوب | تکنسین‌ها و مرمت‌گران موزه | پویانماها و طراحان جلوه‌های ویژه | طراحان بازی‌های ویدیویی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>مطالعه دقیق فیلم‌نامه، نمایشنامه یا اهداف نمایشگاه جهت تدوین کانسپت صحنه | تحقیق در خصوص ویژگی‌های معماری، اقلیمی و سبک‌های تاریخی دوره مورد نظر | تهیه اسکیس‌های مفهومی، نقشه‌های اجرایی، پلان‌های چیدمان و ماکت‌های مقیاسی | برگزاری جلسات هماهنگی با کارگردان، طراح نور، صدابردار و مدیر تولید | برآورد هزینه‌ها، انتخاب متریال‌های سازه‌ای و تدوین بودجه ساخت دکور و غرفه‌ها | نظارت مستقیم بر عملیات ساخت، نصب، رنگ‌آمیزی و ایمنی سازه‌های صحنه | انتخاب و تهیه وسایل صحنه (آکسسوار)، مبلمان، پرده‌ها و جزئیات دکوراتیو | حضور در جلسات تمرین جهت ارزیابی کارایی صحنه با زوایای دوربین و حرکت بازیگران | طراحی و تعبیه تدابیر ایمنی، مسیرهای تردد و ضوابط حفاظتی در غرفه‌ها و صحنه‌ها | هماهنگی برای جمع‌آوری، تفکیک و انبارداری سازه‌ها و وسایل صحنه پس از پایان پروژه</t>
+          <t>تهیه نمونه‌ها یا آثار گرافیکی مورد نیاز برای تکمیل نمایشگاه، یا ترتیب دادن تهیه آن‌ها. | ترتیب دادن قرارداد با پیمانکاران بیرونی برای ساخت سازه‌های نمایشگاهی. | واگذاری وظایف به کارکنان برای تکمیل ایده‌های طراحی و تهیه طرح‌های اولیه، تصویرسازی و نقشه‌های تفصیلی صحنه، یا گرافیک و پویانمایی. | حضور در تمرین‌ها و جلسات تولید برای دریافت و انتقال اطلاعات مرتبط با صحنه. | همکاری با مسئولان نور و صدا تا این جنبه‌های تولید با طراحی صحنه یا چیدمان نمایشگاه هماهنگ شود. | رایزنی با کارفرمایان و کارکنان برای گردآوری اطلاعات درباره فضای نمایشگاه، درون‌مایه و محتوای پیشنهادی، زمان‌بندی، بودجه، مواد یا الزامات تبلیغاتی. | رایزنی با مرمتگران برای تعیین شیوه مدیریت جنبه‌های محیطی نمایشگاه، مانند نور، دما و رطوبت، تا اشیا محافظت شوند و نمایشگاه ارتقا یابد. | هماهنگی برچیدن صحنه‌ها، لوازم صحنه و نمایشگاه‌ها پس از پایان تولید یا رویداد. | هماهنگی حمل صحنه‌هایی که خارج از محل ساخته شده‌اند و هماهنگی برپایی آن‌ها در محل استفاده. | طراحی و ساخت ماکت مقیاس‌دار طرح‌های صحنه، یا صحنه‌های کوچک‌مقیاس مورد استفاده در فیلم‌برداری پس‌زمینه یا جلوه‌های ویژه. | طراحی و تولید ویترین‌ها و موادی که برای تزئین ویترین، چیدمان داخلی یا محل برگزاری رویداد، مانند خیابان‌ها و محوطه‌های نمایشگاهی، به کار می‌روند. | تدوین طرح‌های صحنه، بر پایه ارزیابی فیلم‌نامه، بودجه، اطلاعات پژوهشی و لوکیشن‌های در دسترس. | هدایت و هماهنگی فعالیت‌های ساخت، برپایی یا تزئین برای اطمینان از انطباق صحنه‌ها یا نمایشگاه‌ها با الزامات طراحی، بودجه و زمان‌بندی. | برآورد هزینه‌های مرتبط با صحنه یا نمایشگاه، شامل مواد، ساخت و اجاره لوازم صحنه یا لوکیشن. | بررسی اشیایی که قرار است در نمایشگاه قرار گیرند برای برنامه‌ریزی محل و شیوه نمایش آن‌ها. | گنجاندن سامانه‌های امنیتی در چیدمان نمایشگاه. | بازرسی نمایشگاه‌های برپاشده از نظر انطباق با مشخصات و عملکرد رضایت‌بخش اجزای جلوه‌های ویژه. | مشاهده صحنه‌ها در حین تمرین برای اطمینان از اینکه عناصر صحنه با جنبه‌های اجرایی مانند حرکت بازیگران و زوایای دوربین تداخل ندارند. | برنامه‌ریزی برای مسائل خاص هر مکان، مانند محدودیت فضا، الگوهای رفت‌وآمد و ملاحظات ایمنی. | تهیه پرداخت‌های اولیه نمایشگاه‌های پیشنهادی، شامل مشخصات تفصیلی ساخت، چیدمان و مواد، و نمودارهای مرتبط با جنبه‌هایی مانند جلوه‌های ویژه یا نورپردازی. | تهیه پیش‌نویس‌های اولیه و نقشه‌های اجرایی مقیاس‌دار صحنه، شامل نقشه طبقات، دکور و لوازم صحنه‌ای که باید ساخته شوند. | تهیه مواد پشتیبان برای نمایشگاه‌ها و ویترین‌ها، مانند بسته‌های خبری، تبلیغات، اطلاعیه‌های رسانه‌ای، پوستر، بروشور، کاتالوگ و کارت دعوت. | مطالعه فیلم‌نامه برای تعیین الزامات لوکیشن، صحنه و طراحی. | پژوهش درباره عناصر معماری و سبکی متناسب با دوره تاریخی مورد نظر، و رایزنی با کارشناسان برای کسب اطلاعات در صورت لزوم. | انتخاب و خرید چوب و یراق‌آلات لازم برای ساخت صحنه. | انتخاب لوازم صحنه، مانند مبلمان، تابلو، چراغ و فرش. | ارائه نقشه‌ها برای تأیید و تطبیق آن‌ها با اهداف مورد نظر یا با محدودیت‌های بودجه‌ای و ساخت.</t>
         </is>
       </c>
     </row>
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>طراحی | هنرهای زیبا | زبان انگلیسی | رایانه و الکترونیک | فروش و بازاریابی | تولید و فرآوری | ارتباطات و رسانه | مهندسی و فناوری | مدیریت و امور اداری</t>
+          <t>طراحی | هنرهای زیبا | زبان انگلیسی | رایانه و الکترونیک | فروش و بازاریابی | تولید و فرآوری | ارتباطات و رسانه | مهندسی و فناوری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | اصالت و ابتکار | توجه انتخابی | تسهیم زمان | تجسم فضایی | حفظ کردن | تشخیص رنگ دیداری | چابکی انگشتان</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | تشخیص رنگ بصری | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>طراحان تجاری و صنعتی | طراحان گرافیک | طراحان داخلی | طراحان مد و لباس | طراحان صحنه و نمایشگاه | طراحان گل و گل‌آراها | طراحان دکوراسیون و ویترین مغازه | مدیران هنری | هنرمندان جلوه‌های ویژه و پویانماها | هنرمندان هنرهای تجسمی از جمله نقاشان، مجسمه‌سازان و تصویرگران | هنرمندان صنایع دستی | سایر هنرمندان و مشاغل مرتبط | طراحان وب و رابط کاربری دیجیتال | معماران، به‌جز معماران منظر و سازه‌های دریایی | معماران منظر | مدرسان هنر، تئاتر و موسیقی در آموزش عالی | نقشه‌کشان مکانیک | طراحان بازی‌های ویدئویی | عکاسان | تهیه‌کنندگان و کارگردانان</t>
+          <t>طراحان تجاری و صنعتی | طراحان گرافیک | طراحان داخلی | طراحان مد و پوشاک | طراحان صحنه و نمایشگاه | طراحان گل و گل‌آراها | طراحان دکوراسیون و ویترین مغازه | مدیران هنری | پویانماها و طراحان جلوه‌های ویژه | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | هنرمندان صنایع دستی | سایر هنرمندان و مشاغل مرتبط | طراحان وب و رابط‌های دیجیتال | مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | مهندسان معمار منظر | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | نقشه‌کشان مکانیک | طراحان بازی‌های ویدیویی | عکاسان | تهیه‌کنندگان و کارگردانان</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>طراحی محصولات، فضاها و اقلام بصری در حوزه‌های تخصصی و طبقه‌بندی‌نشده | مشاوره با کارفرمایان جهت تعیین الزامات طراحی، زمان‌بندی و بودجه اجرایی | تحقیق در زمینه متریال‌ها، فناوری‌های نوین، نیازهای کاربر و روندهای بازار | تهیه طرح‌های اولیه دستی، نقشه‌های فنی دقیق و مدل‌های دیجیتال سه‌بعدی | انتخاب رنگ‌ها، متریال‌ها، پرداخت‌های سطحی و قطعات متناسب با طرح | ساخت مدل‌های اولیه و ماکت‌های آزمایشی برای ارزیابی عملکرد و ارگونومی | ارائه پروپوزال‌ها و طرح‌ها به کارفرما و اصلاح آن‌ها بر اساس بازخوردها | هماهنگی و نظارت بر سازندگان، تامین‌کنندگان و تولیدکنندگان در طول فرآیند ساخت | تهیه مستندات فنی، مشخصات اجرایی و برآورد هزینه‌های تولید | انطباق طرح‌ها با استانداردهای کیفی، ضوابط ایمنی و مقررات زیست‌محیطی</t>
+          <t>طراحی محصولات، فضاها و ویترین‌ها در تخصص‌هایی که جداگانه طبقه‌بندی نشده‌اند. | رایزنی با کارفرمایان برای تعیین الزامات طراحی، بودجه و زمان‌بندی. | پژوهش درباره مواد، روش‌ها، روندهای بازار و نیازهای کاربر. | تهیه طرح‌های اولیه ایده، پرداخت‌ها، ماکت‌ها و نقشه‌های فنی. | انتخاب رنگ، مواد، پرداخت‌ها و اجزای طرح. | ساخت نمونه اولیه و ماکت برای ارزیابی ظاهر و کارکرد. | ارائه پیشنهادهای طراحی به کارفرمایان و بازنگری آن‌ها بر پایه بازخورد. | هماهنگی با سازندگان، کارگاه‌ها و تأمین‌کنندگان در جریان تولید. | تهیه مشخصات، برآورد هزینه و مستندات تولید. | بازرسی کار تکمیل‌شده برای راستی‌آزمایی انطباق با هدف طراحی و استانداردهای کیفیت. | حصول اطمینان از انطباق طرح‌ها با الزامات ایمنی، دسترس‌پذیری و مقررات. | نگهداری پرونده‌های طراحی، نمونه مواد و سوابق تأمین‌کنندگان. | پیگیری زمان‌بندی و بودجه پروژه تا تکمیل آن. | تهیه نمونه‌کار و مواد تبلیغاتی برای جذب مشتری.</t>
         </is>
       </c>
     </row>
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | شنیدن فعال | نظارت | تفکر انتقادی</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>هنرهای زیبا | زبان انگلیسی | ارتباطات و رسانه | جامعه‌شناسی و مردم‌شناسی | روان‌شناسی | خدمات مشتریان و خدمات فردی</t>
+          <t>هنرهای زیبا | زبان انگلیسی | ارتباطات و رسانه | جامعه‌شناسی و انسان‌شناسی | روان‌شناسی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | حفظ کردن | وضوح گفتار | اصالت و ابتکار | دید نزدیک | حساسیت به مسئله | توجه انتخابی | روانی ایده‌ها | تشخیص گفتار</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حفظ کردن | وضوح گفتار | اصالت | بینایی نزدیک | حساسیت به مسئله | توجه انتخابی | روانی ایده‌ها | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کارگزاران و مدیران برنامه‌های هنرمندان، مجریان و ورزشکاران | مدیران هنری | مدرسان هنر، تئاتر و موسیقی در آموزش عالی | گویندگان پخش و مجریان رادیویی | طراحان حرکات موزون و رقص‌پردازان | متصدیان لباس صحنه | رقصندگان | تدوینگران فیلم و ویدئو | هنرمندان هنرهای تجسمی از جمله نقاشان، مجسمه‌سازان و تصویرگران | چهره‌پردازان تئاتر و سینما | مدل‌ها و مانکن‌ها | مدیران موسیقی و آهنگسازان | نوازندگان و خوانندگان | تحلیل‌گران اخبار، خبرنگاران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | مدرسان دوره‌های آزاد و توسعهٔ فردی | هنرمندان جلوه‌های ویژه و پویانماها | مدیران انتخاب بازیگر و استعدادیاب‌ها | نویسندگان و پدیدآورندگان</t>
+          <t>مدیران برنامه‌ها و نمایندگان هنرمندان، مجریان و ورزشکاران | مدیران هنری | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | گویندگان پخش و مجریان رادیویی | طراحان حرکت و کوروگراف‌ها | متصدیان و جامه داران لباس صحنه | هنرمندان رقص و حرکات موزون | تدوین‌گران فیلم و ویدیو | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | چهره‌پردازان و گریموران تئاتر و سینما | مدل‌ها | رهبران ارکستر، مدیران موسیقی و آهنگسازان | نوازندگان و خوانندگان | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | پویانماها و طراحان جلوه‌های ویژه | مسئولان انتخاب بازیگر و استعدادیابی | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>شرکت در آزمون‌های انتخاب بازیگر (کستینگ) و تست‌های بازیگری | مطالعه و تحلیل عمیق فیلم‌نامه و نمایشنامه برای شناخت ابعاد شخصیتی نقش | تمرین، یادگیری و از بر کردن دیالوگ‌ها، نشانه‌ها و میزانسن‌های تعیین‌شده | همکاری نزدیک با کارگردان، نویسنده و سایر بازیگران جهت رسیدن به لحن مناسب | اجرای نقش با به‌کارگیری تکنیک‌های بیانی، لحن، حالات چهره و حرکات بدنی | هماهنگی کامل با سایر عوامل صحنه از جمله گریمور، طراح لباس، صدابردار و نورپرداز | حضور منظم و متعهدانه در جلسات دورخوانی، تمرین‌های صحنه و ضبط نهایی | گویندگی، روایتگری یا صداپیشگی برای انیمیشن‌ها، فیلم‌ها و نمایش‌های رادیویی | فراگیری و اجرای حرکات مهارتی، تکنیک‌های بدنی یا بدلکاری‌های سبک تحت نظارت مربی | شرکت در نشست‌های خبری، مصاحبه‌ها و رویدادهای ترویجی جهت معرفی اثر</t>
+          <t>شرکت در آزمون بازیگری و فراخوان انتخاب بازیگر برای دریافت نقش. | همکاری با سایر بازیگران به‌عنوان بخشی از یک گروه اجرایی. | ساخت عروسک و آدمک شکم‌گویی و دوخت لباس‌های جانبی، با ابزارهای دستی و ماشین. | پوشیدن لباس و گریم دلقک و اجرای برنامه‌های کمدی برای سرگرمی تماشاگران. | معرفی اجراها و اجراکنندگان برای برانگیختن شور و هماهنگی گذار روان میان بخش‌های برنامه در رویدادها. | شناخت شخصیت‌های فیلم‌نامه و روابط آنان با یکدیگر برای پرورش برداشت از نقش. | اجرای برداشت‌های طنزآمیز و جدی از احساسات، کنش‌ها و موقعیت‌ها، با استفاده از حرکات بدن، حالات چهره و اشاره. | اجرای شعبده‌های اصیل و متداول برای سرگرم و شگفت‌زده کردن تماشاگران، گاه با مشارکت دادن خود آنان. | ایفا و تفسیر نقش، با استفاده از گفتار، اشاره و حرکات بدن، برای سرگرمی، آگاهی‌بخشی یا آموزش مخاطبان رادیو، سینما، تلویزیون یا اجرای زنده. | آماده‌سازی و اجرای بدل‌کاری برای تولیدات سینمایی، تلویزیونی یا صحنه‌ای. | تبلیغ تولیدات از راه‌هایی مانند مصاحبه درباره نمایش‌ها یا فیلم‌ها. | خواندن از روی فیلم‌نامه یا کتاب برای روایت کنش یا آگاهی‌بخشی و سرگرمی مخاطبان، با استفاده از لوازم صحنه اندک یا بدون آن. | خواندن یا رقصیدن در اجراهای نمایشی یا کمدی. | مطالعه و تمرین نقش از روی فیلم‌نامه برای تفسیر، یادگیری و از بر کردن دیالوگ‌ها، بدل‌کاری‌ها و نشانه‌های صحنه، مطابق دستور کارگردان. | لطیفه‌گویی، اجرای رقص و آواز و نمایش کوتاه کمدی، تقلید رفتار و صدای دیگران، تغییر حالت چهره و به‌کارگیری شگردهای دیگر برای سرگرم کردن تماشاگران. | همکاری نزدیک با کارگردانان، سایر بازیگران و نمایشنامه‌نویسان برای یافتن مناسب‌ترین تفسیر از نقش. | همکاری با سایر عوامل مسئول نور، لباس، گریم و لوازم صحنه. | نگارش متن اصیل یا اقتباسی برای نمایش‌های جدی، کمدی، عروسکی، روایت یا سایر اجراها.</t>
         </is>
       </c>
     </row>
